--- a/scenario_specific_data.xlsx
+++ b/scenario_specific_data.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECAA895-5C8C-4B13-9549-8E12CDF92D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11A7899-3799-4720-A70E-9758303E01D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{135E7A19-983F-4672-B1BC-B86D20613CB6}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" xr2:uid="{135E7A19-983F-4672-B1BC-B86D20613CB6}"/>
   </bookViews>
   <sheets>
-    <sheet name="solar_prices" sheetId="1" r:id="rId1"/>
-    <sheet name="piped_gas_prices" sheetId="2" r:id="rId2"/>
-    <sheet name="lng_prices" sheetId="3" r:id="rId3"/>
+    <sheet name="import_prices" sheetId="1" r:id="rId1"/>
+    <sheet name="manufacturing_prices" sheetId="5" r:id="rId2"/>
+    <sheet name="piped_gas_prices" sheetId="2" r:id="rId3"/>
+    <sheet name="lng_prices" sheetId="3" r:id="rId4"/>
+    <sheet name="piped_gas_trajectory" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
   <si>
     <t>Stf</t>
   </si>
@@ -96,6 +98,153 @@
   <si>
     <t>piped_gas_2049</t>
   </si>
+  <si>
+    <t>gas_dem_2024</t>
+  </si>
+  <si>
+    <t>gas_dem_2029</t>
+  </si>
+  <si>
+    <t>gas_dem_2034</t>
+  </si>
+  <si>
+    <t>gas_dem_2039</t>
+  </si>
+  <si>
+    <t>gas_dem_2044</t>
+  </si>
+  <si>
+    <t>gas_dem_2049</t>
+  </si>
+  <si>
+    <t>Resulting</t>
+  </si>
+  <si>
+    <t>import_EU27_windon_2024</t>
+  </si>
+  <si>
+    <t>import_EU27_windon_2029</t>
+  </si>
+  <si>
+    <t>import_EU27_windon_2034</t>
+  </si>
+  <si>
+    <t>import_EU27_windon_2039</t>
+  </si>
+  <si>
+    <t>import_EU27_windon_2044</t>
+  </si>
+  <si>
+    <t>import_EU27_windon_2049</t>
+  </si>
+  <si>
+    <t>import_EU27_windoff_2024</t>
+  </si>
+  <si>
+    <t>import_EU27_windoff_2029</t>
+  </si>
+  <si>
+    <t>import_EU27_windoff_2034</t>
+  </si>
+  <si>
+    <t>import_EU27_windoff_2039</t>
+  </si>
+  <si>
+    <t>import_EU27_windoff_2044</t>
+  </si>
+  <si>
+    <t>import_EU27_windoff_2049</t>
+  </si>
+  <si>
+    <t>import_EU27_Batteries_2024</t>
+  </si>
+  <si>
+    <t>import_EU27_Batteries_2029</t>
+  </si>
+  <si>
+    <t>import_EU27_Batteries_2034</t>
+  </si>
+  <si>
+    <t>import_EU27_Batteries_2039</t>
+  </si>
+  <si>
+    <t>import_EU27_Batteries_2044</t>
+  </si>
+  <si>
+    <t>import_EU27_Batteries_2049</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_solarPV_2024</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_solarPV_2029</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_solarPV_2034</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_solarPV_2039</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_solarPV_2044</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_solarPV_2049</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windon_2024</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windon_2029</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windon_2034</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windon_2039</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windon_2044</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windon_2049</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windoff_2024</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windoff_2029</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windoff_2034</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windoff_2039</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windoff_2044</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_windoff_2049</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_Batteries_2024</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_Batteries_2029</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_Batteries_2034</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_Batteries_2039</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_Batteries_2044</t>
+  </si>
+  <si>
+    <t>manufacturing_EU27_Batteries_2049</t>
+  </si>
 </sst>
 </file>
 
@@ -142,10 +291,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -161,6 +311,3078 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-AT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>piped_gas_prices!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Resulting</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>piped_gas_prices!$A$2:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>piped_gas_prices!$H$2:$H$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.68</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>20.52</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CD6C-4336-9288-6298CBAEE12D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="75566175"/>
+        <c:axId val="75566655"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="75566175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-AT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="75566655"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="75566655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-AT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="75566175"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-AT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-AT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>lng_prices!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Resulting</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>lng_prices!$A$2:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>lng_prices!$H$2:$H$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>23.62</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.62</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.62</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.62</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23.62</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>29.94</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36.54</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-73B8-4ED3-B07D-29FCC6D3ED78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="494675759"/>
+        <c:axId val="494679119"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="494675759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-AT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="494679119"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="494679119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-AT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="494675759"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-AT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-AT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>piped_gas_trajectory!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Resulting</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>piped_gas_trajectory!$A$2:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>piped_gas_trajectory!$H$2:$H$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>319200000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>319200000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0D08-422D-BAA2-64BA530236C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="418080751"/>
+        <c:axId val="418081711"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="418080751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-AT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="418081711"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="418081711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-AT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="418080751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-AT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>159067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>186690</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2857</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34810379-ABBD-DA10-FB94-6B4203D4A7AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>130492</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>5715</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>155257</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7E2525F-13C4-560D-E608-08603823BF43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>149542</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>710565</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>174307</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F963597F-5271-2970-7EB7-C3A63E7935D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,10 +3702,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD82904F-FA36-4CCF-BBD4-3C4BF0458D10}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,8 +3730,62 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -518,8 +3797,32 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>1052044.8400000001</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2">
+        <v>1775265.6417320003</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2">
+        <v>90210</v>
+      </c>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -531,8 +3834,32 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>1042480.7960000001</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3">
+        <v>1722922.372057667</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3">
+        <v>88856.85</v>
+      </c>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -544,8 +3871,32 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>1032916.7520000001</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4">
+        <v>1670579.1023833335</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4">
+        <v>87523</v>
+      </c>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -557,8 +3908,32 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>1023352.708</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5">
+        <v>1618235.832709</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5">
+        <v>86209.15</v>
+      </c>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -570,8 +3945,32 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>1013788.6639999999</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6">
+        <v>1565892.5630346665</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6">
+        <v>84915.01</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -585,8 +3984,38 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>1004224.62</v>
+      </c>
+      <c r="I7">
+        <v>1004224.62</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7">
+        <v>1513549.293360333</v>
+      </c>
+      <c r="O7">
+        <v>1513549.293360333</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7">
+        <v>83640.289999999994</v>
+      </c>
+      <c r="U7">
+        <v>83640.289999999994</v>
+      </c>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -600,8 +4029,38 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>994660.57600000012</v>
+      </c>
+      <c r="I8">
+        <v>994660.57600000012</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8">
+        <v>1461206.0236859999</v>
+      </c>
+      <c r="O8">
+        <v>1461206.0236859999</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8">
+        <v>82384.69</v>
+      </c>
+      <c r="U8">
+        <v>82384.69</v>
+      </c>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -615,8 +4074,38 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>992747.76720000012</v>
+      </c>
+      <c r="I9">
+        <v>992747.76720000012</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9">
+        <v>1444015.15599508</v>
+      </c>
+      <c r="O9">
+        <v>1444015.15599508</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9">
+        <v>81147.92</v>
+      </c>
+      <c r="U9">
+        <v>81147.92</v>
+      </c>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -630,8 +4119,38 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>990834.9584</v>
+      </c>
+      <c r="I10">
+        <v>990834.9584</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10">
+        <v>1426824.2883041599</v>
+      </c>
+      <c r="O10">
+        <v>1426824.2883041599</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10">
+        <v>79929.7</v>
+      </c>
+      <c r="U10">
+        <v>79929.7</v>
+      </c>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -645,8 +4164,38 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>988922.1496</v>
+      </c>
+      <c r="I11">
+        <v>988922.1496</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11">
+        <v>1409633.42061324</v>
+      </c>
+      <c r="O11">
+        <v>1409633.42061324</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11">
+        <v>78729.759999999995</v>
+      </c>
+      <c r="U11">
+        <v>78729.759999999995</v>
+      </c>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -662,8 +4211,44 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>987009.34079999989</v>
+      </c>
+      <c r="I12">
+        <v>987009.34079999989</v>
+      </c>
+      <c r="J12">
+        <v>987009.34079999989</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12">
+        <v>1392442.5529223196</v>
+      </c>
+      <c r="O12">
+        <v>1392442.5529223196</v>
+      </c>
+      <c r="P12">
+        <v>1392442.5529223196</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12">
+        <v>77547.820000000007</v>
+      </c>
+      <c r="U12">
+        <v>77547.820000000007</v>
+      </c>
+      <c r="V12">
+        <v>77547.820000000007</v>
+      </c>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -679,8 +4264,44 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>985096.53199999989</v>
+      </c>
+      <c r="I13">
+        <v>985096.53199999989</v>
+      </c>
+      <c r="J13">
+        <v>985096.53199999989</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13">
+        <v>1375251.6852313997</v>
+      </c>
+      <c r="O13">
+        <v>1375251.6852313997</v>
+      </c>
+      <c r="P13">
+        <v>1375251.6852313997</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13">
+        <v>76383.600000000006</v>
+      </c>
+      <c r="U13">
+        <v>76383.600000000006</v>
+      </c>
+      <c r="V13">
+        <v>76383.600000000006</v>
+      </c>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -696,8 +4317,44 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>983183.72319999977</v>
+      </c>
+      <c r="I14">
+        <v>983183.72319999977</v>
+      </c>
+      <c r="J14">
+        <v>983183.72319999977</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14">
+        <v>1358060.8175404796</v>
+      </c>
+      <c r="O14">
+        <v>1358060.8175404796</v>
+      </c>
+      <c r="P14">
+        <v>1358060.8175404796</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14">
+        <v>75236.84</v>
+      </c>
+      <c r="U14">
+        <v>75236.84</v>
+      </c>
+      <c r="V14">
+        <v>75236.84</v>
+      </c>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -713,8 +4370,44 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>981270.91439999978</v>
+      </c>
+      <c r="I15">
+        <v>981270.91439999978</v>
+      </c>
+      <c r="J15">
+        <v>981270.91439999978</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15">
+        <v>1340869.9498495597</v>
+      </c>
+      <c r="O15">
+        <v>1340869.9498495597</v>
+      </c>
+      <c r="P15">
+        <v>1340869.9498495597</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15">
+        <v>74107.289999999994</v>
+      </c>
+      <c r="U15">
+        <v>74107.289999999994</v>
+      </c>
+      <c r="V15">
+        <v>74107.289999999994</v>
+      </c>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -730,8 +4423,44 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>979358.10559999966</v>
+      </c>
+      <c r="I16">
+        <v>979358.10559999966</v>
+      </c>
+      <c r="J16">
+        <v>979358.10559999966</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16">
+        <v>1323679.0821586396</v>
+      </c>
+      <c r="O16">
+        <v>1323679.0821586396</v>
+      </c>
+      <c r="P16">
+        <v>1323679.0821586396</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16">
+        <v>72994.679999999993</v>
+      </c>
+      <c r="U16">
+        <v>72994.679999999993</v>
+      </c>
+      <c r="V16">
+        <v>72994.679999999993</v>
+      </c>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -749,8 +4478,50 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>977445.29679999966</v>
+      </c>
+      <c r="I17">
+        <v>977445.29679999966</v>
+      </c>
+      <c r="J17">
+        <v>977445.29679999966</v>
+      </c>
+      <c r="K17">
+        <v>977445.29679999966</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17">
+        <v>1306488.2144677194</v>
+      </c>
+      <c r="O17">
+        <v>1306488.2144677194</v>
+      </c>
+      <c r="P17">
+        <v>1306488.2144677194</v>
+      </c>
+      <c r="Q17">
+        <v>1306488.2144677194</v>
+      </c>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17">
+        <v>71898.759999999995</v>
+      </c>
+      <c r="U17">
+        <v>71898.759999999995</v>
+      </c>
+      <c r="V17">
+        <v>71898.759999999995</v>
+      </c>
+      <c r="W17">
+        <v>71898.759999999995</v>
+      </c>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -768,8 +4539,50 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>975532.48799999955</v>
+      </c>
+      <c r="I18">
+        <v>975532.48799999955</v>
+      </c>
+      <c r="J18">
+        <v>975532.48799999955</v>
+      </c>
+      <c r="K18">
+        <v>975532.48799999955</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18">
+        <v>1288027.7959324</v>
+      </c>
+      <c r="O18">
+        <v>1288027.7959324</v>
+      </c>
+      <c r="P18">
+        <v>1288027.7959324</v>
+      </c>
+      <c r="Q18">
+        <v>1288027.7959324</v>
+      </c>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18">
+        <v>70819.28</v>
+      </c>
+      <c r="U18">
+        <v>70819.28</v>
+      </c>
+      <c r="V18">
+        <v>70819.28</v>
+      </c>
+      <c r="W18">
+        <v>70819.28</v>
+      </c>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -787,8 +4600,50 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>973619.67919999966</v>
+      </c>
+      <c r="I19">
+        <v>973619.67919999966</v>
+      </c>
+      <c r="J19">
+        <v>973619.67919999966</v>
+      </c>
+      <c r="K19">
+        <v>973619.67919999966</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19">
+        <v>1288154.7510168403</v>
+      </c>
+      <c r="O19">
+        <v>1288154.7510168403</v>
+      </c>
+      <c r="P19">
+        <v>1288154.7510168403</v>
+      </c>
+      <c r="Q19">
+        <v>1288154.7510168403</v>
+      </c>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19">
+        <v>69755.990000000005</v>
+      </c>
+      <c r="U19">
+        <v>69755.990000000005</v>
+      </c>
+      <c r="V19">
+        <v>69755.990000000005</v>
+      </c>
+      <c r="W19">
+        <v>69755.990000000005</v>
+      </c>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -806,8 +4661,50 @@
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>971706.87039999955</v>
+      </c>
+      <c r="I20">
+        <v>971706.87039999955</v>
+      </c>
+      <c r="J20">
+        <v>971706.87039999955</v>
+      </c>
+      <c r="K20">
+        <v>971706.87039999955</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20">
+        <v>1288281.7061012802</v>
+      </c>
+      <c r="O20">
+        <v>1288281.7061012802</v>
+      </c>
+      <c r="P20">
+        <v>1288281.7061012802</v>
+      </c>
+      <c r="Q20">
+        <v>1288281.7061012802</v>
+      </c>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20">
+        <v>68708.649999999994</v>
+      </c>
+      <c r="U20">
+        <v>68708.649999999994</v>
+      </c>
+      <c r="V20">
+        <v>68708.649999999994</v>
+      </c>
+      <c r="W20">
+        <v>68708.649999999994</v>
+      </c>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -825,8 +4722,50 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>969794.06159999955</v>
+      </c>
+      <c r="I21">
+        <v>969794.06159999955</v>
+      </c>
+      <c r="J21">
+        <v>969794.06159999955</v>
+      </c>
+      <c r="K21">
+        <v>969794.06159999955</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21">
+        <v>1288408.6611857202</v>
+      </c>
+      <c r="O21">
+        <v>1288408.6611857202</v>
+      </c>
+      <c r="P21">
+        <v>1288408.6611857202</v>
+      </c>
+      <c r="Q21">
+        <v>1288408.6611857202</v>
+      </c>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21">
+        <v>67677.02</v>
+      </c>
+      <c r="U21">
+        <v>67677.02</v>
+      </c>
+      <c r="V21">
+        <v>67677.02</v>
+      </c>
+      <c r="W21">
+        <v>67677.02</v>
+      </c>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -846,8 +4785,56 @@
         <v>184961.50109999999</v>
       </c>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>967881.25279999943</v>
+      </c>
+      <c r="I22">
+        <v>967881.25279999943</v>
+      </c>
+      <c r="J22">
+        <v>967881.25279999943</v>
+      </c>
+      <c r="K22">
+        <v>967881.25279999943</v>
+      </c>
+      <c r="L22">
+        <v>967881.25279999943</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22">
+        <v>1288535.6162701603</v>
+      </c>
+      <c r="O22">
+        <v>1288535.6162701603</v>
+      </c>
+      <c r="P22">
+        <v>1288535.6162701603</v>
+      </c>
+      <c r="Q22">
+        <v>1288535.6162701603</v>
+      </c>
+      <c r="R22">
+        <v>1288535.6162701603</v>
+      </c>
+      <c r="S22" s="2"/>
+      <c r="T22">
+        <v>66660.86</v>
+      </c>
+      <c r="U22">
+        <v>66660.86</v>
+      </c>
+      <c r="V22">
+        <v>66660.86</v>
+      </c>
+      <c r="W22">
+        <v>66660.86</v>
+      </c>
+      <c r="X22">
+        <v>66660.86</v>
+      </c>
+      <c r="Y22" s="2"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -867,8 +4854,56 @@
         <v>182187.07860000001</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>965968.44399999944</v>
+      </c>
+      <c r="I23">
+        <v>965968.44399999944</v>
+      </c>
+      <c r="J23">
+        <v>965968.44399999944</v>
+      </c>
+      <c r="K23">
+        <v>965968.44399999944</v>
+      </c>
+      <c r="L23">
+        <v>965968.44399999944</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23">
+        <v>1288662.5713546001</v>
+      </c>
+      <c r="O23">
+        <v>1288662.5713546001</v>
+      </c>
+      <c r="P23">
+        <v>1288662.5713546001</v>
+      </c>
+      <c r="Q23">
+        <v>1288662.5713546001</v>
+      </c>
+      <c r="R23">
+        <v>1288662.5713546001</v>
+      </c>
+      <c r="S23" s="2"/>
+      <c r="T23">
+        <v>65659.95</v>
+      </c>
+      <c r="U23">
+        <v>65659.95</v>
+      </c>
+      <c r="V23">
+        <v>65659.95</v>
+      </c>
+      <c r="W23">
+        <v>65659.95</v>
+      </c>
+      <c r="X23">
+        <v>65659.95</v>
+      </c>
+      <c r="Y23" s="2"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -888,8 +4923,56 @@
         <v>179454.27239999999</v>
       </c>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>964055.63519999932</v>
+      </c>
+      <c r="I24">
+        <v>964055.63519999932</v>
+      </c>
+      <c r="J24">
+        <v>964055.63519999932</v>
+      </c>
+      <c r="K24">
+        <v>964055.63519999932</v>
+      </c>
+      <c r="L24">
+        <v>964055.63519999932</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24">
+        <v>1288789.5264390404</v>
+      </c>
+      <c r="O24">
+        <v>1288789.5264390404</v>
+      </c>
+      <c r="P24">
+        <v>1288789.5264390404</v>
+      </c>
+      <c r="Q24">
+        <v>1288789.5264390404</v>
+      </c>
+      <c r="R24">
+        <v>1288789.5264390404</v>
+      </c>
+      <c r="S24" s="2"/>
+      <c r="T24">
+        <v>64674.05</v>
+      </c>
+      <c r="U24">
+        <v>64674.05</v>
+      </c>
+      <c r="V24">
+        <v>64674.05</v>
+      </c>
+      <c r="W24">
+        <v>64674.05</v>
+      </c>
+      <c r="X24">
+        <v>64674.05</v>
+      </c>
+      <c r="Y24" s="2"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -909,8 +4992,56 @@
         <v>176762.4583</v>
       </c>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <v>962142.82639999932</v>
+      </c>
+      <c r="I25">
+        <v>962142.82639999932</v>
+      </c>
+      <c r="J25">
+        <v>962142.82639999932</v>
+      </c>
+      <c r="K25">
+        <v>962142.82639999932</v>
+      </c>
+      <c r="L25">
+        <v>962142.82639999932</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25">
+        <v>1288916.4815234803</v>
+      </c>
+      <c r="O25">
+        <v>1288916.4815234803</v>
+      </c>
+      <c r="P25">
+        <v>1288916.4815234803</v>
+      </c>
+      <c r="Q25">
+        <v>1288916.4815234803</v>
+      </c>
+      <c r="R25">
+        <v>1288916.4815234803</v>
+      </c>
+      <c r="S25" s="2"/>
+      <c r="T25">
+        <v>63702.94</v>
+      </c>
+      <c r="U25">
+        <v>63702.94</v>
+      </c>
+      <c r="V25">
+        <v>63702.94</v>
+      </c>
+      <c r="W25">
+        <v>63702.94</v>
+      </c>
+      <c r="X25">
+        <v>63702.94</v>
+      </c>
+      <c r="Y25" s="2"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -930,8 +5061,56 @@
         <v>174111.0214</v>
       </c>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <v>960230.01759999921</v>
+      </c>
+      <c r="I26">
+        <v>960230.01759999921</v>
+      </c>
+      <c r="J26">
+        <v>960230.01759999921</v>
+      </c>
+      <c r="K26">
+        <v>960230.01759999921</v>
+      </c>
+      <c r="L26">
+        <v>960230.01759999921</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26">
+        <v>1289043.4366079206</v>
+      </c>
+      <c r="O26">
+        <v>1289043.4366079206</v>
+      </c>
+      <c r="P26">
+        <v>1289043.4366079206</v>
+      </c>
+      <c r="Q26">
+        <v>1289043.4366079206</v>
+      </c>
+      <c r="R26">
+        <v>1289043.4366079206</v>
+      </c>
+      <c r="S26" s="2"/>
+      <c r="T26">
+        <v>62746.400000000001</v>
+      </c>
+      <c r="U26">
+        <v>62746.400000000001</v>
+      </c>
+      <c r="V26">
+        <v>62746.400000000001</v>
+      </c>
+      <c r="W26">
+        <v>62746.400000000001</v>
+      </c>
+      <c r="X26">
+        <v>62746.400000000001</v>
+      </c>
+      <c r="Y26" s="2"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -953,8 +5132,62 @@
       <c r="G27">
         <v>171499.3561</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <v>958317.20879999921</v>
+      </c>
+      <c r="I27">
+        <v>958317.20879999921</v>
+      </c>
+      <c r="J27">
+        <v>958317.20879999921</v>
+      </c>
+      <c r="K27">
+        <v>958317.20879999921</v>
+      </c>
+      <c r="L27">
+        <v>958317.20879999921</v>
+      </c>
+      <c r="M27">
+        <v>958317.20879999921</v>
+      </c>
+      <c r="N27">
+        <v>1289170.3916923604</v>
+      </c>
+      <c r="O27">
+        <v>1289170.3916923604</v>
+      </c>
+      <c r="P27">
+        <v>1289170.3916923604</v>
+      </c>
+      <c r="Q27">
+        <v>1289170.3916923604</v>
+      </c>
+      <c r="R27">
+        <v>1289170.3916923604</v>
+      </c>
+      <c r="S27">
+        <v>1289170.3916923604</v>
+      </c>
+      <c r="T27">
+        <v>61804.2</v>
+      </c>
+      <c r="U27">
+        <v>61804.2</v>
+      </c>
+      <c r="V27">
+        <v>61804.2</v>
+      </c>
+      <c r="W27">
+        <v>61804.2</v>
+      </c>
+      <c r="X27">
+        <v>61804.2</v>
+      </c>
+      <c r="Y27">
+        <v>61804.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -976,512 +5209,1628 @@
       <c r="G28">
         <v>168926.8658</v>
       </c>
+      <c r="H28">
+        <v>956404.40000000026</v>
+      </c>
+      <c r="I28">
+        <v>956404.40000000026</v>
+      </c>
+      <c r="J28">
+        <v>956404.40000000026</v>
+      </c>
+      <c r="K28">
+        <v>956404.40000000026</v>
+      </c>
+      <c r="L28">
+        <v>956404.40000000026</v>
+      </c>
+      <c r="M28">
+        <v>956404.40000000026</v>
+      </c>
+      <c r="N28">
+        <v>1289297.3467768</v>
+      </c>
+      <c r="O28">
+        <v>1289297.3467768</v>
+      </c>
+      <c r="P28">
+        <v>1289297.3467768</v>
+      </c>
+      <c r="Q28">
+        <v>1289297.3467768</v>
+      </c>
+      <c r="R28">
+        <v>1289297.3467768</v>
+      </c>
+      <c r="S28">
+        <v>1289297.3467768</v>
+      </c>
+      <c r="T28">
+        <v>60876.14</v>
+      </c>
+      <c r="U28">
+        <v>60876.14</v>
+      </c>
+      <c r="V28">
+        <v>60876.14</v>
+      </c>
+      <c r="W28">
+        <v>60876.14</v>
+      </c>
+      <c r="X28">
+        <v>60876.14</v>
+      </c>
+      <c r="Y28">
+        <v>60876.14</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L23:L38">
-    <sortCondition ref="L23:L38"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K23:K38">
+    <sortCondition ref="K23:K38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2930297B-B8C6-4229-B09A-A1848D4D7BAF}">
-  <dimension ref="A1:G28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7094D60-577C-43F3-97BF-857EEFCA39B5}">
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1" t="s">
+        <v>64</v>
+      </c>
+      <c r="W1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>22.68</v>
+        <v>303600</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>1673707.7</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2">
+        <v>2337972.5216000001</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="3">
+        <v>129380</v>
+      </c>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>22.68</v>
+        <v>299045.40000000002</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>1660955.6413333334</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3">
+        <v>2318026.381866667</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="3">
+        <v>127438.3</v>
+      </c>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>22.68</v>
+        <v>294559.71899999998</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>1648203.5826666667</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4">
+        <v>2298080.2421333333</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="3">
+        <v>125526.73</v>
+      </c>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>22.68</v>
+        <v>290141.32319999998</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>1635451.524</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5">
+        <v>2278134.1023999997</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="3">
+        <v>123644.83</v>
+      </c>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>22.68</v>
+        <v>285788.2034</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>1622699.4653333335</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6">
+        <v>2258187.9626666661</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="3">
+        <v>121792.16</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>22.68</v>
+        <v>281498.4804</v>
       </c>
       <c r="C7">
-        <v>22.68</v>
+        <v>281498.4804</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>1609947.4066666667</v>
+      </c>
+      <c r="I7">
+        <v>1609947.4066666667</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7">
+        <v>2238241.8229333302</v>
+      </c>
+      <c r="O7">
+        <v>2238241.8229333302</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="3">
+        <v>119968.28</v>
+      </c>
+      <c r="U7" s="3">
+        <v>119968.28</v>
+      </c>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>22.68</v>
+        <v>277270.34419999999</v>
       </c>
       <c r="C8">
-        <v>22.68</v>
+        <v>277270.34419999999</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>1597195.3480000002</v>
+      </c>
+      <c r="I8">
+        <v>1597195.3480000002</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8">
+        <v>2218295.6831999999</v>
+      </c>
+      <c r="O8">
+        <v>2218295.6831999999</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="3">
+        <v>118172.75</v>
+      </c>
+      <c r="U8" s="3">
+        <v>118172.75</v>
+      </c>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>22.68</v>
+        <v>273102.28909999999</v>
       </c>
       <c r="C9">
-        <v>22.68</v>
+        <v>273102.28909999999</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>1594326.1348000003</v>
+      </c>
+      <c r="I9">
+        <v>1594326.1348000003</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9">
+        <v>2205259.4561600001</v>
+      </c>
+      <c r="O9">
+        <v>2205259.4561600001</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="3">
+        <v>116405.16</v>
+      </c>
+      <c r="U9" s="3">
+        <v>116405.16</v>
+      </c>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>22.68</v>
+        <v>268993.2548</v>
       </c>
       <c r="C10">
-        <v>22.68</v>
+        <v>268993.2548</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>1591456.9216000002</v>
+      </c>
+      <c r="I10">
+        <v>1591456.9216000002</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10">
+        <v>2192223.2291199998</v>
+      </c>
+      <c r="O10">
+        <v>2192223.2291199998</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="3">
+        <v>114665.09</v>
+      </c>
+      <c r="U10" s="3">
+        <v>114665.09</v>
+      </c>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>22.68</v>
+        <v>264942.41499999998</v>
       </c>
       <c r="C11">
-        <v>22.68</v>
+        <v>264942.41499999998</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>1588587.7084000004</v>
+      </c>
+      <c r="I11">
+        <v>1588587.7084000004</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11">
+        <v>2179187.0020799995</v>
+      </c>
+      <c r="O11">
+        <v>2179187.0020799995</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="3">
+        <v>112952.12</v>
+      </c>
+      <c r="U11" s="3">
+        <v>112952.12</v>
+      </c>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>22.68</v>
+        <v>260948.7948</v>
       </c>
       <c r="C12">
-        <v>22.68</v>
+        <v>260948.7948</v>
       </c>
       <c r="D12">
-        <v>22.68</v>
+        <v>260948.7948</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>1585718.4952000002</v>
+      </c>
+      <c r="I12">
+        <v>1585718.4952000002</v>
+      </c>
+      <c r="J12">
+        <v>1585718.4952000002</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12">
+        <v>2166150.7750399997</v>
+      </c>
+      <c r="O12">
+        <v>2166150.7750399997</v>
+      </c>
+      <c r="P12">
+        <v>2166150.7750399997</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="3">
+        <v>111265.84</v>
+      </c>
+      <c r="U12" s="3">
+        <v>111265.84</v>
+      </c>
+      <c r="V12" s="3">
+        <v>111265.84</v>
+      </c>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>22.68</v>
+        <v>257011.4613</v>
       </c>
       <c r="C13">
-        <v>22.68</v>
+        <v>257011.4613</v>
       </c>
       <c r="D13">
-        <v>22.68</v>
+        <v>257011.4613</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>1582849.2820000004</v>
+      </c>
+      <c r="I13">
+        <v>1582849.2820000004</v>
+      </c>
+      <c r="J13">
+        <v>1582849.2820000004</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13">
+        <v>2153114.5479999995</v>
+      </c>
+      <c r="O13">
+        <v>2153114.5479999995</v>
+      </c>
+      <c r="P13">
+        <v>2153114.5479999995</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="3">
+        <v>109605.86</v>
+      </c>
+      <c r="U13" s="3">
+        <v>109605.86</v>
+      </c>
+      <c r="V13" s="3">
+        <v>109605.86</v>
+      </c>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>22.68</v>
+        <v>253129.39139999999</v>
       </c>
       <c r="C14">
-        <v>22.68</v>
+        <v>253129.39139999999</v>
       </c>
       <c r="D14">
-        <v>22.68</v>
+        <v>253129.39139999999</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>1579980.0688000005</v>
+      </c>
+      <c r="I14">
+        <v>1579980.0688000005</v>
+      </c>
+      <c r="J14">
+        <v>1579980.0688000005</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14">
+        <v>2140078.3209599997</v>
+      </c>
+      <c r="O14">
+        <v>2140078.3209599997</v>
+      </c>
+      <c r="P14">
+        <v>2140078.3209599997</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="3">
+        <v>107971.77</v>
+      </c>
+      <c r="U14" s="3">
+        <v>107971.77</v>
+      </c>
+      <c r="V14" s="3">
+        <v>107971.77</v>
+      </c>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>22.68</v>
+        <v>249301.63759999999</v>
       </c>
       <c r="C15">
-        <v>22.68</v>
+        <v>249301.63759999999</v>
       </c>
       <c r="D15">
-        <v>22.68</v>
+        <v>249301.63759999999</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>1577110.8556000004</v>
+      </c>
+      <c r="I15">
+        <v>1577110.8556000004</v>
+      </c>
+      <c r="J15">
+        <v>1577110.8556000004</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15">
+        <v>2127042.0939199994</v>
+      </c>
+      <c r="O15">
+        <v>2127042.0939199994</v>
+      </c>
+      <c r="P15">
+        <v>2127042.0939199994</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15">
+        <v>106363.2</v>
+      </c>
+      <c r="U15">
+        <v>106363.2</v>
+      </c>
+      <c r="V15">
+        <v>106363.2</v>
+      </c>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>22.68</v>
+        <v>245527.30809999999</v>
       </c>
       <c r="C16">
-        <v>22.68</v>
+        <v>245527.30809999999</v>
       </c>
       <c r="D16">
-        <v>22.68</v>
+        <v>245527.30809999999</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>1574241.6424000005</v>
+      </c>
+      <c r="I16">
+        <v>1574241.6424000005</v>
+      </c>
+      <c r="J16">
+        <v>1574241.6424000005</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16">
+        <v>2114005.8668799992</v>
+      </c>
+      <c r="O16">
+        <v>2114005.8668799992</v>
+      </c>
+      <c r="P16">
+        <v>2114005.8668799992</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16">
+        <v>104779.75</v>
+      </c>
+      <c r="U16">
+        <v>104779.75</v>
+      </c>
+      <c r="V16">
+        <v>104779.75</v>
+      </c>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>22.68</v>
+        <v>241805.39859999999</v>
       </c>
       <c r="C17">
-        <v>22.68</v>
+        <v>241805.39859999999</v>
       </c>
       <c r="D17">
-        <v>22.68</v>
+        <v>241805.39859999999</v>
       </c>
       <c r="E17">
-        <v>22.68</v>
+        <v>241805.39859999999</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>1571372.4292000004</v>
+      </c>
+      <c r="I17">
+        <v>1571372.4292000004</v>
+      </c>
+      <c r="J17">
+        <v>1571372.4292000004</v>
+      </c>
+      <c r="K17">
+        <v>1571372.4292000004</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17">
+        <v>2100969.6398399994</v>
+      </c>
+      <c r="O17">
+        <v>2100969.6398399994</v>
+      </c>
+      <c r="P17">
+        <v>2100969.6398399994</v>
+      </c>
+      <c r="Q17">
+        <v>2100969.6398399994</v>
+      </c>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17">
+        <v>103221.06</v>
+      </c>
+      <c r="U17">
+        <v>103221.06</v>
+      </c>
+      <c r="V17">
+        <v>103221.06</v>
+      </c>
+      <c r="W17">
+        <v>103221.06</v>
+      </c>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>20.52</v>
+        <v>238134.9901</v>
       </c>
       <c r="C18">
-        <v>20.52</v>
+        <v>238134.9901</v>
       </c>
       <c r="D18">
-        <v>20.52</v>
+        <v>238134.9901</v>
       </c>
       <c r="E18">
-        <v>20.52</v>
+        <v>238134.9901</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>1568503.2160000005</v>
+      </c>
+      <c r="I18">
+        <v>1568503.2160000005</v>
+      </c>
+      <c r="J18">
+        <v>1568503.2160000005</v>
+      </c>
+      <c r="K18">
+        <v>1568503.2160000005</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18">
+        <v>2087933.4128</v>
+      </c>
+      <c r="O18">
+        <v>2087933.4128</v>
+      </c>
+      <c r="P18">
+        <v>2087933.4128</v>
+      </c>
+      <c r="Q18">
+        <v>2087933.4128</v>
+      </c>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18">
+        <v>101686.74</v>
+      </c>
+      <c r="U18">
+        <v>101686.74</v>
+      </c>
+      <c r="V18">
+        <v>101686.74</v>
+      </c>
+      <c r="W18">
+        <v>101686.74</v>
+      </c>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>20.52</v>
+        <v>234515.065</v>
       </c>
       <c r="C19">
-        <v>20.52</v>
+        <v>234515.065</v>
       </c>
       <c r="D19">
-        <v>20.52</v>
+        <v>234515.065</v>
       </c>
       <c r="E19">
-        <v>20.52</v>
+        <v>234515.065</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>1565634.0028000006</v>
+      </c>
+      <c r="I19">
+        <v>1565634.0028000006</v>
+      </c>
+      <c r="J19">
+        <v>1565634.0028000006</v>
+      </c>
+      <c r="K19">
+        <v>1565634.0028000006</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19">
+        <v>2076927.41784</v>
+      </c>
+      <c r="O19">
+        <v>2076927.41784</v>
+      </c>
+      <c r="P19">
+        <v>2076927.41784</v>
+      </c>
+      <c r="Q19">
+        <v>2076927.41784</v>
+      </c>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19">
+        <v>100176.44</v>
+      </c>
+      <c r="U19">
+        <v>100176.44</v>
+      </c>
+      <c r="V19">
+        <v>100176.44</v>
+      </c>
+      <c r="W19">
+        <v>100176.44</v>
+      </c>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>20.52</v>
+        <v>230944.68799999999</v>
       </c>
       <c r="C20">
-        <v>20.52</v>
+        <v>230944.68799999999</v>
       </c>
       <c r="D20">
-        <v>20.52</v>
+        <v>230944.68799999999</v>
       </c>
       <c r="E20">
-        <v>20.52</v>
+        <v>230944.68799999999</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>1562764.7896000005</v>
+      </c>
+      <c r="I20">
+        <v>1562764.7896000005</v>
+      </c>
+      <c r="J20">
+        <v>1562764.7896000005</v>
+      </c>
+      <c r="K20">
+        <v>1562764.7896000005</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20">
+        <v>2065921.4228800002</v>
+      </c>
+      <c r="O20">
+        <v>2065921.4228800002</v>
+      </c>
+      <c r="P20">
+        <v>2065921.4228800002</v>
+      </c>
+      <c r="Q20">
+        <v>2065921.4228800002</v>
+      </c>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20">
+        <v>98689.79</v>
+      </c>
+      <c r="U20">
+        <v>98689.79</v>
+      </c>
+      <c r="V20">
+        <v>98689.79</v>
+      </c>
+      <c r="W20">
+        <v>98689.79</v>
+      </c>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>20.52</v>
+        <v>227422.96530000001</v>
       </c>
       <c r="C21">
-        <v>20.52</v>
+        <v>227422.96530000001</v>
       </c>
       <c r="D21">
-        <v>20.52</v>
+        <v>227422.96530000001</v>
       </c>
       <c r="E21">
-        <v>20.52</v>
+        <v>227422.96530000001</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>1559895.5764000006</v>
+      </c>
+      <c r="I21">
+        <v>1559895.5764000006</v>
+      </c>
+      <c r="J21">
+        <v>1559895.5764000006</v>
+      </c>
+      <c r="K21">
+        <v>1559895.5764000006</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21">
+        <v>2054915.4279200002</v>
+      </c>
+      <c r="O21">
+        <v>2054915.4279200002</v>
+      </c>
+      <c r="P21">
+        <v>2054915.4279200002</v>
+      </c>
+      <c r="Q21">
+        <v>2054915.4279200002</v>
+      </c>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21">
+        <v>97226.44</v>
+      </c>
+      <c r="U21">
+        <v>97226.44</v>
+      </c>
+      <c r="V21">
+        <v>97226.44</v>
+      </c>
+      <c r="W21">
+        <v>97226.44</v>
+      </c>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>20.52</v>
+        <v>223948.88099999999</v>
       </c>
       <c r="C22">
-        <v>20.52</v>
+        <v>223948.88099999999</v>
       </c>
       <c r="D22">
-        <v>20.52</v>
+        <v>223948.88099999999</v>
       </c>
       <c r="E22">
-        <v>20.52</v>
+        <v>223948.88099999999</v>
       </c>
       <c r="F22">
-        <v>20.52</v>
+        <v>223948.88099999999</v>
       </c>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>1557026.3632000005</v>
+      </c>
+      <c r="I22">
+        <v>1557026.3632000005</v>
+      </c>
+      <c r="J22">
+        <v>1557026.3632000005</v>
+      </c>
+      <c r="K22">
+        <v>1557026.3632000005</v>
+      </c>
+      <c r="L22">
+        <v>1557026.3632000005</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22">
+        <v>2043909.4329600004</v>
+      </c>
+      <c r="O22">
+        <v>2043909.4329600004</v>
+      </c>
+      <c r="P22">
+        <v>2043909.4329600004</v>
+      </c>
+      <c r="Q22">
+        <v>2043909.4329600004</v>
+      </c>
+      <c r="R22">
+        <v>2043909.4329600004</v>
+      </c>
+      <c r="S22" s="2"/>
+      <c r="T22">
+        <v>95786.05</v>
+      </c>
+      <c r="U22">
+        <v>95786.05</v>
+      </c>
+      <c r="V22">
+        <v>95786.05</v>
+      </c>
+      <c r="W22">
+        <v>95786.05</v>
+      </c>
+      <c r="X22">
+        <v>95786.05</v>
+      </c>
+      <c r="Y22" s="2"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>20.52</v>
+        <v>220521.46350000001</v>
       </c>
       <c r="C23">
-        <v>20.52</v>
+        <v>220521.46350000001</v>
       </c>
       <c r="D23">
-        <v>20.52</v>
+        <v>220521.46350000001</v>
       </c>
       <c r="E23">
-        <v>20.52</v>
+        <v>220521.46350000001</v>
       </c>
       <c r="F23">
-        <v>20.52</v>
+        <v>220521.46350000001</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>1554157.1500000006</v>
+      </c>
+      <c r="I23">
+        <v>1554157.1500000006</v>
+      </c>
+      <c r="J23">
+        <v>1554157.1500000006</v>
+      </c>
+      <c r="K23">
+        <v>1554157.1500000006</v>
+      </c>
+      <c r="L23">
+        <v>1554157.1500000006</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23">
+        <v>2032903.4380000005</v>
+      </c>
+      <c r="O23">
+        <v>2032903.4380000005</v>
+      </c>
+      <c r="P23">
+        <v>2032903.4380000005</v>
+      </c>
+      <c r="Q23">
+        <v>2032903.4380000005</v>
+      </c>
+      <c r="R23">
+        <v>2032903.4380000005</v>
+      </c>
+      <c r="S23" s="2"/>
+      <c r="T23">
+        <v>94368.26</v>
+      </c>
+      <c r="U23">
+        <v>94368.26</v>
+      </c>
+      <c r="V23">
+        <v>94368.26</v>
+      </c>
+      <c r="W23">
+        <v>94368.26</v>
+      </c>
+      <c r="X23">
+        <v>94368.26</v>
+      </c>
+      <c r="Y23" s="2"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>20.52</v>
+        <v>217139.74350000001</v>
       </c>
       <c r="C24">
-        <v>20.52</v>
+        <v>217139.74350000001</v>
       </c>
       <c r="D24">
-        <v>20.52</v>
+        <v>217139.74350000001</v>
       </c>
       <c r="E24">
-        <v>20.52</v>
+        <v>217139.74350000001</v>
       </c>
       <c r="F24">
-        <v>20.52</v>
+        <v>217139.74350000001</v>
       </c>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>1551287.9368000007</v>
+      </c>
+      <c r="I24">
+        <v>1551287.9368000007</v>
+      </c>
+      <c r="J24">
+        <v>1551287.9368000007</v>
+      </c>
+      <c r="K24">
+        <v>1551287.9368000007</v>
+      </c>
+      <c r="L24">
+        <v>1551287.9368000007</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24">
+        <v>2021897.4430400007</v>
+      </c>
+      <c r="O24">
+        <v>2021897.4430400007</v>
+      </c>
+      <c r="P24">
+        <v>2021897.4430400007</v>
+      </c>
+      <c r="Q24">
+        <v>2021897.4430400007</v>
+      </c>
+      <c r="R24">
+        <v>2021897.4430400007</v>
+      </c>
+      <c r="S24" s="2"/>
+      <c r="T24">
+        <v>92972.74</v>
+      </c>
+      <c r="U24">
+        <v>92972.74</v>
+      </c>
+      <c r="V24">
+        <v>92972.74</v>
+      </c>
+      <c r="W24">
+        <v>92972.74</v>
+      </c>
+      <c r="X24">
+        <v>92972.74</v>
+      </c>
+      <c r="Y24" s="2"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>20.52</v>
+        <v>213802.75769999999</v>
       </c>
       <c r="C25">
-        <v>20.52</v>
+        <v>213802.75769999999</v>
       </c>
       <c r="D25">
-        <v>20.52</v>
+        <v>213802.75769999999</v>
       </c>
       <c r="E25">
-        <v>20.52</v>
+        <v>213802.75769999999</v>
       </c>
       <c r="F25">
-        <v>20.52</v>
+        <v>213802.75769999999</v>
       </c>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <v>1548418.7236000006</v>
+      </c>
+      <c r="I25">
+        <v>1548418.7236000006</v>
+      </c>
+      <c r="J25">
+        <v>1548418.7236000006</v>
+      </c>
+      <c r="K25">
+        <v>1548418.7236000006</v>
+      </c>
+      <c r="L25">
+        <v>1548418.7236000006</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25">
+        <v>2010891.4480800009</v>
+      </c>
+      <c r="O25">
+        <v>2010891.4480800009</v>
+      </c>
+      <c r="P25">
+        <v>2010891.4480800009</v>
+      </c>
+      <c r="Q25">
+        <v>2010891.4480800009</v>
+      </c>
+      <c r="R25">
+        <v>2010891.4480800009</v>
+      </c>
+      <c r="S25" s="2"/>
+      <c r="T25">
+        <v>91599.15</v>
+      </c>
+      <c r="U25">
+        <v>91599.15</v>
+      </c>
+      <c r="V25">
+        <v>91599.15</v>
+      </c>
+      <c r="W25">
+        <v>91599.15</v>
+      </c>
+      <c r="X25">
+        <v>91599.15</v>
+      </c>
+      <c r="Y25" s="2"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>20.52</v>
+        <v>210509.61679999999</v>
       </c>
       <c r="C26">
-        <v>20.52</v>
+        <v>210509.61679999999</v>
       </c>
       <c r="D26">
-        <v>20.52</v>
+        <v>210509.61679999999</v>
       </c>
       <c r="E26">
-        <v>20.52</v>
+        <v>210509.61679999999</v>
       </c>
       <c r="F26">
-        <v>20.52</v>
+        <v>210509.61679999999</v>
       </c>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <v>1545549.5104000007</v>
+      </c>
+      <c r="I26">
+        <v>1545549.5104000007</v>
+      </c>
+      <c r="J26">
+        <v>1545549.5104000007</v>
+      </c>
+      <c r="K26">
+        <v>1545549.5104000007</v>
+      </c>
+      <c r="L26">
+        <v>1545549.5104000007</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26">
+        <v>1999885.4531200009</v>
+      </c>
+      <c r="O26">
+        <v>1999885.4531200009</v>
+      </c>
+      <c r="P26">
+        <v>1999885.4531200009</v>
+      </c>
+      <c r="Q26">
+        <v>1999885.4531200009</v>
+      </c>
+      <c r="R26">
+        <v>1999885.4531200009</v>
+      </c>
+      <c r="S26" s="2"/>
+      <c r="T26">
+        <v>90247.16</v>
+      </c>
+      <c r="U26">
+        <v>90247.16</v>
+      </c>
+      <c r="V26">
+        <v>90247.16</v>
+      </c>
+      <c r="W26">
+        <v>90247.16</v>
+      </c>
+      <c r="X26">
+        <v>90247.16</v>
+      </c>
+      <c r="Y26" s="2"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>20.52</v>
+        <v>207259.3126</v>
       </c>
       <c r="C27">
-        <v>20.52</v>
+        <v>207259.3126</v>
       </c>
       <c r="D27">
-        <v>20.52</v>
+        <v>207259.3126</v>
       </c>
       <c r="E27">
-        <v>20.52</v>
+        <v>207259.3126</v>
       </c>
       <c r="F27">
-        <v>20.52</v>
+        <v>207259.3126</v>
       </c>
       <c r="G27">
-        <v>20.52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>207259.3126</v>
+      </c>
+      <c r="H27">
+        <v>1542680.2972000006</v>
+      </c>
+      <c r="I27">
+        <v>1542680.2972000006</v>
+      </c>
+      <c r="J27">
+        <v>1542680.2972000006</v>
+      </c>
+      <c r="K27">
+        <v>1542680.2972000006</v>
+      </c>
+      <c r="L27">
+        <v>1542680.2972000006</v>
+      </c>
+      <c r="M27">
+        <v>1542680.2972000006</v>
+      </c>
+      <c r="N27">
+        <v>1988879.4581600011</v>
+      </c>
+      <c r="O27">
+        <v>1988879.4581600011</v>
+      </c>
+      <c r="P27">
+        <v>1988879.4581600011</v>
+      </c>
+      <c r="Q27">
+        <v>1988879.4581600011</v>
+      </c>
+      <c r="R27">
+        <v>1988879.4581600011</v>
+      </c>
+      <c r="S27">
+        <v>1988879.4581600011</v>
+      </c>
+      <c r="T27">
+        <v>88916.45</v>
+      </c>
+      <c r="U27">
+        <v>88916.45</v>
+      </c>
+      <c r="V27">
+        <v>88916.45</v>
+      </c>
+      <c r="W27">
+        <v>88916.45</v>
+      </c>
+      <c r="X27">
+        <v>88916.45</v>
+      </c>
+      <c r="Y27">
+        <v>88916.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>204050.9535</v>
       </c>
       <c r="C28">
-        <v>18</v>
+        <v>204050.9535</v>
       </c>
       <c r="D28">
-        <v>18</v>
+        <v>204050.9535</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>204050.9535</v>
       </c>
       <c r="F28">
-        <v>18</v>
+        <v>204050.9535</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>204050.9535</v>
+      </c>
+      <c r="H28">
+        <v>1539811.0840000003</v>
+      </c>
+      <c r="I28">
+        <v>1539811.0840000003</v>
+      </c>
+      <c r="J28">
+        <v>1539811.0840000003</v>
+      </c>
+      <c r="K28">
+        <v>1539811.0840000003</v>
+      </c>
+      <c r="L28">
+        <v>1539811.0840000003</v>
+      </c>
+      <c r="M28">
+        <v>1539811.0840000003</v>
+      </c>
+      <c r="N28">
+        <v>1977873.4631999999</v>
+      </c>
+      <c r="O28">
+        <v>1977873.4631999999</v>
+      </c>
+      <c r="P28">
+        <v>1977873.4631999999</v>
+      </c>
+      <c r="Q28">
+        <v>1977873.4631999999</v>
+      </c>
+      <c r="R28">
+        <v>1977873.4631999999</v>
+      </c>
+      <c r="S28">
+        <v>1977873.4631999999</v>
+      </c>
+      <c r="T28">
+        <v>87606.7</v>
+      </c>
+      <c r="U28">
+        <v>87606.7</v>
+      </c>
+      <c r="V28">
+        <v>87606.7</v>
+      </c>
+      <c r="W28">
+        <v>87606.7</v>
+      </c>
+      <c r="X28">
+        <v>87606.7</v>
+      </c>
+      <c r="Y28">
+        <v>87606.7</v>
       </c>
     </row>
   </sheetData>
@@ -1490,262 +6839,941 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B22E9F6-210C-4B51-BC39-95E792B1A10E}">
-  <dimension ref="A1:G28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2930297B-B8C6-4229-B09A-A1848D4D7BAF}">
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
-      <c r="B2" s="1">
-        <v>23.62</v>
+      <c r="B2">
+        <v>22.68</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <f>B2</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
-      <c r="B3" s="1">
-        <v>23.62</v>
+      <c r="B3">
+        <v>22.68</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <f t="shared" ref="H3:H5" si="0">B3</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
-      <c r="B4" s="1">
-        <v>23.62</v>
+      <c r="B4">
+        <v>22.68</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
-      <c r="B5" s="1">
-        <v>23.62</v>
+      <c r="B5">
+        <v>22.68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
-      <c r="B6" s="1">
-        <v>23.62</v>
+      <c r="B6">
+        <v>22.68</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <f>B6</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
-      <c r="B7" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="C7" s="1">
-        <v>23.62</v>
+      <c r="B7">
+        <v>22.68</v>
+      </c>
+      <c r="C7">
+        <v>22.68</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <f>C7</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
-      <c r="B8" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C8" s="1">
-        <v>29.94</v>
+      <c r="B8">
+        <v>22.68</v>
+      </c>
+      <c r="C8">
+        <v>22.68</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <f t="shared" ref="H8:H10" si="1">C8</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
-      <c r="B9" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C9" s="1">
-        <v>29.94</v>
+      <c r="B9">
+        <v>22.68</v>
+      </c>
+      <c r="C9">
+        <v>22.68</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
-      <c r="B10" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C10" s="1">
-        <v>29.94</v>
+      <c r="B10">
+        <v>22.68</v>
+      </c>
+      <c r="C10">
+        <v>22.68</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
-      <c r="B11" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C11" s="1">
-        <v>29.94</v>
+      <c r="B11">
+        <v>22.68</v>
+      </c>
+      <c r="C11">
+        <v>22.68</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f>C11</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
-      <c r="B12" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C12" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D12" s="1">
-        <v>29.94</v>
+      <c r="B12">
+        <v>22.68</v>
+      </c>
+      <c r="C12">
+        <v>22.68</v>
+      </c>
+      <c r="D12">
+        <v>22.68</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <f>D12</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
-      <c r="B13" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C13" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D13" s="1">
-        <v>29.94</v>
+      <c r="B13">
+        <v>22.68</v>
+      </c>
+      <c r="C13">
+        <v>22.68</v>
+      </c>
+      <c r="D13">
+        <v>22.68</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <f t="shared" ref="H13:H16" si="2">D13</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
-      <c r="B14" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C14" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D14" s="1">
-        <v>29.94</v>
+      <c r="B14">
+        <v>22.68</v>
+      </c>
+      <c r="C14">
+        <v>22.68</v>
+      </c>
+      <c r="D14">
+        <v>22.68</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
-      <c r="B15" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C15" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D15" s="1">
-        <v>29.94</v>
+      <c r="B15">
+        <v>22.68</v>
+      </c>
+      <c r="C15">
+        <v>22.68</v>
+      </c>
+      <c r="D15">
+        <v>22.68</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
-      <c r="B16" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C16" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D16" s="1">
-        <v>29.94</v>
+      <c r="B16">
+        <v>22.68</v>
+      </c>
+      <c r="C16">
+        <v>22.68</v>
+      </c>
+      <c r="D16">
+        <v>22.68</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
+      <c r="B17">
+        <v>22.68</v>
+      </c>
+      <c r="C17">
+        <v>22.68</v>
+      </c>
+      <c r="D17">
+        <v>22.68</v>
+      </c>
+      <c r="E17">
+        <v>22.68</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17">
+        <f>E17</f>
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>20.52</v>
+      </c>
+      <c r="C18">
+        <v>20.52</v>
+      </c>
+      <c r="D18">
+        <v>20.52</v>
+      </c>
+      <c r="E18">
+        <v>20.52</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18">
+        <f t="shared" ref="H18:H21" si="3">E18</f>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>20.52</v>
+      </c>
+      <c r="C19">
+        <v>20.52</v>
+      </c>
+      <c r="D19">
+        <v>20.52</v>
+      </c>
+      <c r="E19">
+        <v>20.52</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>20.52</v>
+      </c>
+      <c r="C20">
+        <v>20.52</v>
+      </c>
+      <c r="D20">
+        <v>20.52</v>
+      </c>
+      <c r="E20">
+        <v>20.52</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>20.52</v>
+      </c>
+      <c r="C21">
+        <v>20.52</v>
+      </c>
+      <c r="D21">
+        <v>20.52</v>
+      </c>
+      <c r="E21">
+        <v>20.52</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>20.52</v>
+      </c>
+      <c r="C22">
+        <v>20.52</v>
+      </c>
+      <c r="D22">
+        <v>20.52</v>
+      </c>
+      <c r="E22">
+        <v>20.52</v>
+      </c>
+      <c r="F22">
+        <v>20.52</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22">
+        <f>F22</f>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>20.52</v>
+      </c>
+      <c r="C23">
+        <v>20.52</v>
+      </c>
+      <c r="D23">
+        <v>20.52</v>
+      </c>
+      <c r="E23">
+        <v>20.52</v>
+      </c>
+      <c r="F23">
+        <v>20.52</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23">
+        <f t="shared" ref="H23:H26" si="4">F23</f>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>20.52</v>
+      </c>
+      <c r="C24">
+        <v>20.52</v>
+      </c>
+      <c r="D24">
+        <v>20.52</v>
+      </c>
+      <c r="E24">
+        <v>20.52</v>
+      </c>
+      <c r="F24">
+        <v>20.52</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24">
+        <f t="shared" si="4"/>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>20.52</v>
+      </c>
+      <c r="C25">
+        <v>20.52</v>
+      </c>
+      <c r="D25">
+        <v>20.52</v>
+      </c>
+      <c r="E25">
+        <v>20.52</v>
+      </c>
+      <c r="F25">
+        <v>20.52</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25">
+        <f t="shared" si="4"/>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>20.52</v>
+      </c>
+      <c r="C26">
+        <v>20.52</v>
+      </c>
+      <c r="D26">
+        <v>20.52</v>
+      </c>
+      <c r="E26">
+        <v>20.52</v>
+      </c>
+      <c r="F26">
+        <v>20.52</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>20.52</v>
+      </c>
+      <c r="C27">
+        <v>20.52</v>
+      </c>
+      <c r="D27">
+        <v>20.52</v>
+      </c>
+      <c r="E27">
+        <v>20.52</v>
+      </c>
+      <c r="F27">
+        <v>20.52</v>
+      </c>
+      <c r="G27">
+        <v>20.52</v>
+      </c>
+      <c r="H27">
+        <f>G27</f>
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>18</v>
+      </c>
+      <c r="C28">
+        <v>18</v>
+      </c>
+      <c r="D28">
+        <v>18</v>
+      </c>
+      <c r="E28">
+        <v>18</v>
+      </c>
+      <c r="F28">
+        <v>18</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28">
+        <f>G28</f>
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B22E9F6-210C-4B51-BC39-95E792B1A10E}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="1">
+        <v>23.62</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2">
+        <f>B2</f>
+        <v>23.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="1">
+        <v>23.62</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3">
+        <f t="shared" ref="H3:H5" si="0">B3</f>
+        <v>23.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="1">
+        <v>23.62</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>23.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2027</v>
+      </c>
+      <c r="B5" s="1">
+        <v>23.62</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>23.62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2028</v>
+      </c>
+      <c r="B6" s="1">
+        <v>23.62</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6">
+        <f>B6</f>
+        <v>23.62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2029</v>
+      </c>
+      <c r="B7" s="1">
+        <v>23.62</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23.62</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7">
+        <f>C7</f>
+        <v>23.62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2030</v>
+      </c>
+      <c r="B8" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C8" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8">
+        <f t="shared" ref="H8:H10" si="1">C8</f>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2031</v>
+      </c>
+      <c r="B9" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C9" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2032</v>
+      </c>
+      <c r="B10" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C10" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2033</v>
+      </c>
+      <c r="B11" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C11" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11">
+        <f>C11</f>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2034</v>
+      </c>
+      <c r="B12" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C12" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D12" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12">
+        <f>D12</f>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2035</v>
+      </c>
+      <c r="B13" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C13" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D13" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13">
+        <f t="shared" ref="H13:H16" si="2">D13</f>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2036</v>
+      </c>
+      <c r="B14" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C14" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D14" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2037</v>
+      </c>
+      <c r="B15" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C15" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D15" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2038</v>
+      </c>
+      <c r="B16" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="C16" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="D16" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2039</v>
+      </c>
       <c r="B17" s="1">
         <v>29.94</v>
       </c>
@@ -1760,8 +7788,12 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <f>E17</f>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -1779,8 +7811,12 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <f t="shared" ref="H18:H21" si="3">E18</f>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -1798,8 +7834,12 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -1817,8 +7857,12 @@
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -1836,8 +7880,12 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -1857,8 +7905,12 @@
         <v>36.54</v>
       </c>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <f>F22</f>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -1878,8 +7930,12 @@
         <v>36.54</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <f t="shared" ref="H23:H26" si="4">F23</f>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -1899,8 +7955,12 @@
         <v>36.54</v>
       </c>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <f t="shared" si="4"/>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -1920,8 +7980,12 @@
         <v>36.54</v>
       </c>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <f t="shared" si="4"/>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -1941,8 +8005,12 @@
         <v>36.54</v>
       </c>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -1964,8 +8032,12 @@
       <c r="G27" s="1">
         <v>36.54</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <f>G27</f>
+        <v>36.54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -1987,8 +8059,629 @@
       <c r="G28" s="1">
         <v>36.54</v>
       </c>
+      <c r="H28">
+        <f>G28</f>
+        <v>36.54</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F4AA74-F6E7-4E96-8A8A-2DCFA03A93AC}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>319200000</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2">
+        <f>B2</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>319200000</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3">
+        <f t="shared" ref="H3:H5" si="0">B3</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>319200000</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2027</v>
+      </c>
+      <c r="B5">
+        <v>319200000</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2028</v>
+      </c>
+      <c r="B6">
+        <v>319200000</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6">
+        <f>B6</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2029</v>
+      </c>
+      <c r="B7">
+        <v>319200000</v>
+      </c>
+      <c r="C7">
+        <v>319200000</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7">
+        <f>C7</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>319200000</v>
+      </c>
+      <c r="C8">
+        <v>319200000</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8">
+        <f t="shared" ref="H8:H10" si="1">C8</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2031</v>
+      </c>
+      <c r="B9">
+        <v>319200000</v>
+      </c>
+      <c r="C9">
+        <v>319200000</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2032</v>
+      </c>
+      <c r="B10">
+        <v>319200000</v>
+      </c>
+      <c r="C10">
+        <v>319200000</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2033</v>
+      </c>
+      <c r="B11">
+        <v>319200000</v>
+      </c>
+      <c r="C11">
+        <v>319200000</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11">
+        <f>C11</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2034</v>
+      </c>
+      <c r="B12">
+        <v>319200000</v>
+      </c>
+      <c r="C12">
+        <v>319200000</v>
+      </c>
+      <c r="D12">
+        <v>319200000</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12">
+        <f>D12</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2035</v>
+      </c>
+      <c r="B13">
+        <v>319200000</v>
+      </c>
+      <c r="C13">
+        <v>319200000</v>
+      </c>
+      <c r="D13">
+        <v>319200000</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13">
+        <f t="shared" ref="H13:H16" si="2">D13</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2036</v>
+      </c>
+      <c r="B14">
+        <v>319200000</v>
+      </c>
+      <c r="C14">
+        <v>319200000</v>
+      </c>
+      <c r="D14">
+        <v>319200000</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2037</v>
+      </c>
+      <c r="B15">
+        <v>319200000</v>
+      </c>
+      <c r="C15">
+        <v>319200000</v>
+      </c>
+      <c r="D15">
+        <v>319200000</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2038</v>
+      </c>
+      <c r="B16">
+        <v>319200000</v>
+      </c>
+      <c r="C16">
+        <v>319200000</v>
+      </c>
+      <c r="D16">
+        <v>319200000</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2039</v>
+      </c>
+      <c r="B17">
+        <v>319200000</v>
+      </c>
+      <c r="C17">
+        <v>319200000</v>
+      </c>
+      <c r="D17">
+        <v>319200000</v>
+      </c>
+      <c r="E17">
+        <v>319200000</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17">
+        <f>E17</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>319200000</v>
+      </c>
+      <c r="C18">
+        <v>319200000</v>
+      </c>
+      <c r="D18">
+        <v>319200000</v>
+      </c>
+      <c r="E18">
+        <v>319200000</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18">
+        <f t="shared" ref="H18:H21" si="3">E18</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>319200000</v>
+      </c>
+      <c r="C19">
+        <v>319200000</v>
+      </c>
+      <c r="D19">
+        <v>319200000</v>
+      </c>
+      <c r="E19">
+        <v>319200000</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>319200000</v>
+      </c>
+      <c r="C20">
+        <v>319200000</v>
+      </c>
+      <c r="D20">
+        <v>319200000</v>
+      </c>
+      <c r="E20">
+        <v>319200000</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>319200000</v>
+      </c>
+      <c r="C21">
+        <v>319200000</v>
+      </c>
+      <c r="D21">
+        <v>319200000</v>
+      </c>
+      <c r="E21">
+        <v>319200000</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>319200000</v>
+      </c>
+      <c r="C22">
+        <v>319200000</v>
+      </c>
+      <c r="D22">
+        <v>319200000</v>
+      </c>
+      <c r="E22">
+        <v>319200000</v>
+      </c>
+      <c r="F22">
+        <v>319200000</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22">
+        <f>F22</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>319200000</v>
+      </c>
+      <c r="C23">
+        <v>319200000</v>
+      </c>
+      <c r="D23">
+        <v>319200000</v>
+      </c>
+      <c r="E23">
+        <v>319200000</v>
+      </c>
+      <c r="F23">
+        <v>319200000</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23">
+        <f t="shared" ref="H23:H26" si="4">F23</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>319200000</v>
+      </c>
+      <c r="C24">
+        <v>319200000</v>
+      </c>
+      <c r="D24">
+        <v>319200000</v>
+      </c>
+      <c r="E24">
+        <v>319200000</v>
+      </c>
+      <c r="F24">
+        <v>319200000</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24">
+        <f t="shared" si="4"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>319200000</v>
+      </c>
+      <c r="C25">
+        <v>319200000</v>
+      </c>
+      <c r="D25">
+        <v>319200000</v>
+      </c>
+      <c r="E25">
+        <v>319200000</v>
+      </c>
+      <c r="F25">
+        <v>319200000</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25">
+        <f t="shared" si="4"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>319200000</v>
+      </c>
+      <c r="C26">
+        <v>319200000</v>
+      </c>
+      <c r="D26">
+        <v>319200000</v>
+      </c>
+      <c r="E26">
+        <v>319200000</v>
+      </c>
+      <c r="F26">
+        <v>319200000</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>319200000</v>
+      </c>
+      <c r="C27">
+        <v>319200000</v>
+      </c>
+      <c r="D27">
+        <v>319200000</v>
+      </c>
+      <c r="E27">
+        <v>319200000</v>
+      </c>
+      <c r="F27">
+        <v>319200000</v>
+      </c>
+      <c r="G27">
+        <v>319200000</v>
+      </c>
+      <c r="H27">
+        <f>G27</f>
+        <v>319200000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>319200000</v>
+      </c>
+      <c r="C28">
+        <v>319200000</v>
+      </c>
+      <c r="D28">
+        <v>319200000</v>
+      </c>
+      <c r="E28">
+        <v>319200000</v>
+      </c>
+      <c r="F28">
+        <v>319200000</v>
+      </c>
+      <c r="G28">
+        <v>319200000</v>
+      </c>
+      <c r="H28">
+        <f>G28</f>
+        <v>319200000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/scenario_specific_data.xlsx
+++ b/scenario_specific_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11A7899-3799-4720-A70E-9758303E01D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214930D9-C62F-4C29-88E9-B7A761B5F755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" xr2:uid="{135E7A19-983F-4672-B1BC-B86D20613CB6}"/>
+    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{135E7A19-983F-4672-B1BC-B86D20613CB6}"/>
   </bookViews>
   <sheets>
     <sheet name="import_prices" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="piped_gas_prices" sheetId="2" r:id="rId3"/>
     <sheet name="lng_prices" sheetId="3" r:id="rId4"/>
     <sheet name="piped_gas_trajectory" sheetId="4" r:id="rId5"/>
+    <sheet name="elec_demand" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
   <si>
     <t>Stf</t>
   </si>
@@ -245,6 +246,24 @@
   <si>
     <t>manufacturing_EU27_Batteries_2049</t>
   </si>
+  <si>
+    <t>elec_dem_2024</t>
+  </si>
+  <si>
+    <t>elec_dem_2029</t>
+  </si>
+  <si>
+    <t>elec_dem_2034</t>
+  </si>
+  <si>
+    <t>elec_dem_2039</t>
+  </si>
+  <si>
+    <t>elec_dem_2044</t>
+  </si>
+  <si>
+    <t>elec_dem_2049</t>
+  </si>
 </sst>
 </file>
 
@@ -291,10 +310,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3792,35 +3814,15 @@
       <c r="B2">
         <v>250240</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2">
         <v>1052044.8400000001</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
       <c r="N2">
         <v>1775265.6417320003</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
       <c r="T2">
-        <v>90210</v>
-      </c>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
+        <v>280439.83</v>
+      </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -3829,35 +3831,15 @@
       <c r="B3">
         <v>246486.39999999999</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
       <c r="H3">
         <v>1042480.7960000001</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
       <c r="N3">
         <v>1722922.372057667</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
       <c r="T3">
-        <v>88856.85</v>
-      </c>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
+        <v>274754.90999999997</v>
+      </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -3866,35 +3848,15 @@
       <c r="B4">
         <v>242789.10399999999</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
       <c r="H4">
         <v>1032916.7520000001</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
       <c r="N4">
         <v>1670579.1023833335</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
       <c r="T4">
-        <v>87523</v>
-      </c>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
+        <v>269179.44</v>
+      </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -3903,35 +3865,15 @@
       <c r="B5">
         <v>239147.26740000001</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
       <c r="H5">
         <v>1023352.708</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
       <c r="N5">
         <v>1618235.832709</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
       <c r="T5">
-        <v>86209.15</v>
-      </c>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
+        <v>263711.78000000003</v>
+      </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -3940,35 +3882,15 @@
       <c r="B6">
         <v>235560.05840000001</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
       <c r="H6">
         <v>1013788.6639999999</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
       <c r="N6">
         <v>1565892.5630346665</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
       <c r="T6">
-        <v>84915.01</v>
-      </c>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
+        <v>258350.32</v>
+      </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -3980,40 +3902,24 @@
       <c r="C7">
         <v>232026.65760000001</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
       <c r="H7">
         <v>1004224.62</v>
       </c>
       <c r="I7">
         <v>1004224.62</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
       <c r="N7">
         <v>1513549.293360333</v>
       </c>
       <c r="O7">
         <v>1513549.293360333</v>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
       <c r="T7">
-        <v>83640.289999999994</v>
+        <v>253093.46</v>
       </c>
       <c r="U7">
-        <v>83640.289999999994</v>
-      </c>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
+        <v>253093.46</v>
+      </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -4023,42 +3929,26 @@
         <v>228546.25769999999</v>
       </c>
       <c r="C8">
-        <v>228546.25769999999</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+        <v>278546.25770000002</v>
+      </c>
       <c r="H8">
         <v>994660.57600000012</v>
       </c>
       <c r="I8">
-        <v>994660.57600000012</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+        <v>1044660.576</v>
+      </c>
       <c r="N8">
         <v>1461206.0236859999</v>
       </c>
       <c r="O8">
-        <v>1461206.0236859999</v>
-      </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+        <v>1511206.024</v>
+      </c>
       <c r="T8">
-        <v>82384.69</v>
+        <v>247939.65</v>
       </c>
       <c r="U8">
-        <v>82384.69</v>
-      </c>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
+        <v>297939.65000000002</v>
+      </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -4068,42 +3958,26 @@
         <v>225118.0638</v>
       </c>
       <c r="C9">
-        <v>225118.0638</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+        <v>275118.0638</v>
+      </c>
       <c r="H9">
         <v>992747.76720000012</v>
       </c>
       <c r="I9">
-        <v>992747.76720000012</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+        <v>1042747.7672</v>
+      </c>
       <c r="N9">
         <v>1444015.15599508</v>
       </c>
       <c r="O9">
-        <v>1444015.15599508</v>
-      </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+        <v>1494015.156</v>
+      </c>
       <c r="T9">
-        <v>81147.92</v>
+        <v>242887.37</v>
       </c>
       <c r="U9">
-        <v>81147.92</v>
-      </c>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
+        <v>292887.37</v>
+      </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -4113,42 +3987,26 @@
         <v>221741.2929</v>
       </c>
       <c r="C10">
-        <v>221741.2929</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+        <v>271741.2929</v>
+      </c>
       <c r="H10">
         <v>990834.9584</v>
       </c>
       <c r="I10">
-        <v>990834.9584</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+        <v>1040834.9584</v>
+      </c>
       <c r="N10">
         <v>1426824.2883041599</v>
       </c>
       <c r="O10">
-        <v>1426824.2883041599</v>
-      </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+        <v>1476824.2879999999</v>
+      </c>
       <c r="T10">
-        <v>79929.7</v>
+        <v>237935.1</v>
       </c>
       <c r="U10">
-        <v>79929.7</v>
-      </c>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
+        <v>287935.09999999998</v>
+      </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -4158,42 +4016,26 @@
         <v>218415.1735</v>
       </c>
       <c r="C11">
-        <v>218415.1735</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+        <v>268415.17349999998</v>
+      </c>
       <c r="H11">
         <v>988922.1496</v>
       </c>
       <c r="I11">
-        <v>988922.1496</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+        <v>1038922.1496</v>
+      </c>
       <c r="N11">
         <v>1409633.42061324</v>
       </c>
       <c r="O11">
-        <v>1409633.42061324</v>
-      </c>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
+        <v>1459633.4210000001</v>
+      </c>
       <c r="T11">
-        <v>78729.759999999995</v>
+        <v>233081.4</v>
       </c>
       <c r="U11">
-        <v>78729.759999999995</v>
-      </c>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
+        <v>283081.40000000002</v>
+      </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -4203,50 +4045,38 @@
         <v>215138.94589999999</v>
       </c>
       <c r="C12">
-        <v>215138.94589999999</v>
+        <v>265138.94589999999</v>
       </c>
       <c r="D12">
         <v>215138.94589999999</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
       <c r="H12">
         <v>987009.34079999989</v>
       </c>
       <c r="I12">
-        <v>987009.34079999989</v>
-      </c>
-      <c r="J12">
-        <v>987009.34079999989</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+        <v>1037009.3408</v>
+      </c>
+      <c r="J12" s="4">
+        <v>987009.34</v>
+      </c>
       <c r="N12">
         <v>1392442.5529223196</v>
       </c>
       <c r="O12">
-        <v>1392442.5529223196</v>
+        <v>1442442.5530000001</v>
       </c>
       <c r="P12">
         <v>1392442.5529223196</v>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
       <c r="T12">
-        <v>77547.820000000007</v>
+        <v>228324.82</v>
       </c>
       <c r="U12">
-        <v>77547.820000000007</v>
+        <v>278324.82</v>
       </c>
       <c r="V12">
-        <v>77547.820000000007</v>
-      </c>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
+        <v>228324.82</v>
+      </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -4256,50 +4086,38 @@
         <v>211911.86170000001</v>
       </c>
       <c r="C13">
-        <v>211911.86170000001</v>
+        <v>261911.86170000001</v>
       </c>
       <c r="D13">
-        <v>211911.86170000001</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+        <v>317867.79255000001</v>
+      </c>
       <c r="H13">
         <v>985096.53199999989</v>
       </c>
       <c r="I13">
-        <v>985096.53199999989</v>
-      </c>
-      <c r="J13">
-        <v>985096.53199999989</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+        <v>1035096.532</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1477644.798</v>
+      </c>
       <c r="N13">
         <v>1375251.6852313997</v>
       </c>
       <c r="O13">
-        <v>1375251.6852313997</v>
+        <v>1425251.6850000001</v>
       </c>
       <c r="P13">
-        <v>1375251.6852313997</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
+        <v>2062877.5275000001</v>
+      </c>
       <c r="T13">
-        <v>76383.600000000006</v>
+        <v>223663.91</v>
       </c>
       <c r="U13">
-        <v>76383.600000000006</v>
+        <v>273663.90999999997</v>
       </c>
       <c r="V13">
-        <v>76383.600000000006</v>
-      </c>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
+        <v>335495.86499999999</v>
+      </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -4309,50 +4127,38 @@
         <v>208733.1838</v>
       </c>
       <c r="C14">
-        <v>208733.1838</v>
+        <v>258733.1838</v>
       </c>
       <c r="D14">
-        <v>208733.1838</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+        <v>313099.7757</v>
+      </c>
       <c r="H14">
         <v>983183.72319999977</v>
       </c>
       <c r="I14">
-        <v>983183.72319999977</v>
-      </c>
-      <c r="J14">
-        <v>983183.72319999977</v>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+        <v>1033183.7232</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1474775.5848000001</v>
+      </c>
       <c r="N14">
         <v>1358060.8175404796</v>
       </c>
       <c r="O14">
-        <v>1358060.8175404796</v>
+        <v>1408060.818</v>
       </c>
       <c r="P14">
-        <v>1358060.8175404796</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+        <v>2037091.227</v>
+      </c>
       <c r="T14">
-        <v>75236.84</v>
+        <v>219097.32</v>
       </c>
       <c r="U14">
-        <v>75236.84</v>
+        <v>269097.32</v>
       </c>
       <c r="V14">
-        <v>75236.84</v>
-      </c>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
+        <v>328645.98</v>
+      </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -4362,50 +4168,38 @@
         <v>205602.18599999999</v>
       </c>
       <c r="C15">
-        <v>205602.18599999999</v>
+        <v>255602.18599999999</v>
       </c>
       <c r="D15">
-        <v>205602.18599999999</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+        <v>308403.27899999998</v>
+      </c>
       <c r="H15">
         <v>981270.91439999978</v>
       </c>
       <c r="I15">
-        <v>981270.91439999978</v>
-      </c>
-      <c r="J15">
-        <v>981270.91439999978</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+        <v>1031270.9144</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1471906.3716</v>
+      </c>
       <c r="N15">
         <v>1340869.9498495597</v>
       </c>
       <c r="O15">
-        <v>1340869.9498495597</v>
+        <v>1390869.95</v>
       </c>
       <c r="P15">
-        <v>1340869.9498495597</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+        <v>2011304.925</v>
+      </c>
       <c r="T15">
-        <v>74107.289999999994</v>
+        <v>214623.65</v>
       </c>
       <c r="U15">
-        <v>74107.289999999994</v>
+        <v>264623.65000000002</v>
       </c>
       <c r="V15">
-        <v>74107.289999999994</v>
-      </c>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
+        <v>321935.47499999998</v>
+      </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -4415,50 +4209,38 @@
         <v>202518.1532</v>
       </c>
       <c r="C16">
-        <v>202518.1532</v>
+        <v>252518.1532</v>
       </c>
       <c r="D16">
-        <v>202518.1532</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+        <v>303777.22979999997</v>
+      </c>
       <c r="H16">
         <v>979358.10559999966</v>
       </c>
       <c r="I16">
-        <v>979358.10559999966</v>
-      </c>
-      <c r="J16">
-        <v>979358.10559999966</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+        <v>1029358.1056</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1469037.1584000001</v>
+      </c>
       <c r="N16">
         <v>1323679.0821586396</v>
       </c>
       <c r="O16">
-        <v>1323679.0821586396</v>
+        <v>1373679.0819999999</v>
       </c>
       <c r="P16">
-        <v>1323679.0821586396</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
+        <v>1985518.6229999999</v>
+      </c>
       <c r="T16">
-        <v>72994.679999999993</v>
+        <v>210241.6</v>
       </c>
       <c r="U16">
-        <v>72994.679999999993</v>
+        <v>260241.6</v>
       </c>
       <c r="V16">
-        <v>72994.679999999993</v>
-      </c>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
+        <v>315362.40000000002</v>
+      </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -4468,58 +4250,50 @@
         <v>199480.38089999999</v>
       </c>
       <c r="C17">
-        <v>199480.38089999999</v>
+        <v>249480.38089999999</v>
       </c>
       <c r="D17">
-        <v>199480.38089999999</v>
+        <v>299220.57134999998</v>
       </c>
       <c r="E17">
-        <v>199480.38089999999</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+        <v>299220.57134999998</v>
+      </c>
       <c r="H17">
         <v>977445.29679999966</v>
       </c>
       <c r="I17">
-        <v>977445.29679999966</v>
-      </c>
-      <c r="J17">
-        <v>977445.29679999966</v>
-      </c>
-      <c r="K17">
-        <v>977445.29679999966</v>
-      </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+        <v>1027445.2968</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1466167.9452</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1466167.9452</v>
+      </c>
       <c r="N17">
         <v>1306488.2144677194</v>
       </c>
       <c r="O17">
-        <v>1306488.2144677194</v>
+        <v>1356488.2139999999</v>
       </c>
       <c r="P17">
-        <v>1306488.2144677194</v>
+        <v>1959732.321</v>
       </c>
       <c r="Q17">
-        <v>1306488.2144677194</v>
-      </c>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
+        <v>1959732.321</v>
+      </c>
       <c r="T17">
-        <v>71898.759999999995</v>
+        <v>205949.84</v>
       </c>
       <c r="U17">
-        <v>71898.759999999995</v>
+        <v>255949.84</v>
       </c>
       <c r="V17">
-        <v>71898.759999999995</v>
+        <v>308924.76</v>
       </c>
       <c r="W17">
-        <v>71898.759999999995</v>
-      </c>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
+        <v>308924.76</v>
+      </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -4529,58 +4303,50 @@
         <v>196488.1752</v>
       </c>
       <c r="C18">
-        <v>196488.1752</v>
+        <v>246488.1752</v>
       </c>
       <c r="D18">
-        <v>196488.1752</v>
+        <v>294732.26280000003</v>
       </c>
       <c r="E18">
-        <v>196488.1752</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+        <v>294732.26280000003</v>
+      </c>
       <c r="H18">
         <v>975532.48799999955</v>
       </c>
       <c r="I18">
-        <v>975532.48799999955</v>
-      </c>
-      <c r="J18">
-        <v>975532.48799999955</v>
-      </c>
-      <c r="K18">
-        <v>975532.48799999955</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+        <v>1025532.488</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1463298.7320000001</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1463298.7320000001</v>
+      </c>
       <c r="N18">
         <v>1288027.7959324</v>
       </c>
       <c r="O18">
-        <v>1288027.7959324</v>
+        <v>1338027.7960000001</v>
       </c>
       <c r="P18">
-        <v>1288027.7959324</v>
+        <v>1932041.6939999999</v>
       </c>
       <c r="Q18">
-        <v>1288027.7959324</v>
-      </c>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
+        <v>1932041.6939999999</v>
+      </c>
       <c r="T18">
-        <v>70819.28</v>
+        <v>201747.12</v>
       </c>
       <c r="U18">
-        <v>70819.28</v>
+        <v>251747.12</v>
       </c>
       <c r="V18">
-        <v>70819.28</v>
+        <v>302620.68</v>
       </c>
       <c r="W18">
-        <v>70819.28</v>
-      </c>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
+        <v>302620.68</v>
+      </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -4590,58 +4356,50 @@
         <v>193540.85260000001</v>
       </c>
       <c r="C19">
-        <v>193540.85260000001</v>
+        <v>243540.85260000001</v>
       </c>
       <c r="D19">
-        <v>193540.85260000001</v>
+        <v>290311.27889999998</v>
       </c>
       <c r="E19">
-        <v>193540.85260000001</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+        <v>290311.27889999998</v>
+      </c>
       <c r="H19">
         <v>973619.67919999966</v>
       </c>
       <c r="I19">
-        <v>973619.67919999966</v>
-      </c>
-      <c r="J19">
-        <v>973619.67919999966</v>
-      </c>
-      <c r="K19">
-        <v>973619.67919999966</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+        <v>1023619.6792</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1460429.52</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1460429.52</v>
+      </c>
       <c r="N19">
         <v>1288154.7510168403</v>
       </c>
       <c r="O19">
-        <v>1288154.7510168403</v>
+        <v>1338154.7509999999</v>
       </c>
       <c r="P19">
-        <v>1288154.7510168403</v>
+        <v>1932232.1265</v>
       </c>
       <c r="Q19">
-        <v>1288154.7510168403</v>
-      </c>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
+        <v>1932232.1265</v>
+      </c>
       <c r="T19">
-        <v>69755.990000000005</v>
+        <v>197632.19</v>
       </c>
       <c r="U19">
-        <v>69755.990000000005</v>
+        <v>247632.19</v>
       </c>
       <c r="V19">
-        <v>69755.990000000005</v>
+        <v>296448.28499999997</v>
       </c>
       <c r="W19">
-        <v>69755.990000000005</v>
-      </c>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
+        <v>296448.28499999997</v>
+      </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -4651,58 +4409,50 @@
         <v>190637.73980000001</v>
       </c>
       <c r="C20">
-        <v>190637.73980000001</v>
+        <v>240637.73980000001</v>
       </c>
       <c r="D20">
-        <v>190637.73980000001</v>
+        <v>285956.60969999997</v>
       </c>
       <c r="E20">
-        <v>190637.73980000001</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+        <v>285956.60969999997</v>
+      </c>
       <c r="H20">
         <v>971706.87039999955</v>
       </c>
       <c r="I20">
-        <v>971706.87039999955</v>
-      </c>
-      <c r="J20">
-        <v>971706.87039999955</v>
-      </c>
-      <c r="K20">
-        <v>971706.87039999955</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+        <v>1021706.8704</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1457560.3056000001</v>
+      </c>
+      <c r="K20" s="4">
+        <v>1457560.3056000001</v>
+      </c>
       <c r="N20">
         <v>1288281.7061012802</v>
       </c>
       <c r="O20">
-        <v>1288281.7061012802</v>
+        <v>1338281.706</v>
       </c>
       <c r="P20">
-        <v>1288281.7061012802</v>
+        <v>1932422.5589999999</v>
       </c>
       <c r="Q20">
-        <v>1288281.7061012802</v>
-      </c>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
+        <v>1932422.5589999999</v>
+      </c>
       <c r="T20">
-        <v>68708.649999999994</v>
+        <v>193603.83</v>
       </c>
       <c r="U20">
-        <v>68708.649999999994</v>
+        <v>243603.83</v>
       </c>
       <c r="V20">
-        <v>68708.649999999994</v>
+        <v>290405.745</v>
       </c>
       <c r="W20">
-        <v>68708.649999999994</v>
-      </c>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
+        <v>290405.745</v>
+      </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -4712,58 +4462,50 @@
         <v>187778.17370000001</v>
       </c>
       <c r="C21">
-        <v>187778.17370000001</v>
+        <v>237778.17370000001</v>
       </c>
       <c r="D21">
-        <v>187778.17370000001</v>
+        <v>281667.26055000001</v>
       </c>
       <c r="E21">
-        <v>187778.17370000001</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+        <v>281667.26055000001</v>
+      </c>
       <c r="H21">
         <v>969794.06159999955</v>
       </c>
       <c r="I21">
-        <v>969794.06159999955</v>
-      </c>
-      <c r="J21">
-        <v>969794.06159999955</v>
-      </c>
-      <c r="K21">
-        <v>969794.06159999955</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+        <v>1019794.0616</v>
+      </c>
+      <c r="J21" s="4">
+        <v>1454691.0924</v>
+      </c>
+      <c r="K21" s="4">
+        <v>1454691.0924</v>
+      </c>
       <c r="N21">
         <v>1288408.6611857202</v>
       </c>
       <c r="O21">
-        <v>1288408.6611857202</v>
+        <v>1338408.6610000001</v>
       </c>
       <c r="P21">
-        <v>1288408.6611857202</v>
+        <v>1932612.9915</v>
       </c>
       <c r="Q21">
-        <v>1288408.6611857202</v>
-      </c>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
+        <v>1932612.9915</v>
+      </c>
       <c r="T21">
-        <v>67677.02</v>
+        <v>189660.87</v>
       </c>
       <c r="U21">
-        <v>67677.02</v>
+        <v>239660.87</v>
       </c>
       <c r="V21">
-        <v>67677.02</v>
+        <v>284491.30499999999</v>
       </c>
       <c r="W21">
-        <v>67677.02</v>
-      </c>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
+        <v>284491.30499999999</v>
+      </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -4773,66 +4515,62 @@
         <v>184961.50109999999</v>
       </c>
       <c r="C22">
-        <v>184961.50109999999</v>
+        <v>234961.50109999999</v>
       </c>
       <c r="D22">
-        <v>184961.50109999999</v>
+        <v>277442.25164999999</v>
       </c>
       <c r="E22">
-        <v>184961.50109999999</v>
+        <v>277442.25164999999</v>
       </c>
       <c r="F22">
-        <v>184961.50109999999</v>
-      </c>
-      <c r="G22" s="2"/>
+        <v>277442.25164999999</v>
+      </c>
       <c r="H22">
         <v>967881.25279999943</v>
       </c>
       <c r="I22">
-        <v>967881.25279999943</v>
-      </c>
-      <c r="J22">
-        <v>967881.25279999943</v>
-      </c>
-      <c r="K22">
-        <v>967881.25279999943</v>
-      </c>
-      <c r="L22">
-        <v>967881.25279999943</v>
-      </c>
-      <c r="M22" s="2"/>
+        <v>1017881.2528</v>
+      </c>
+      <c r="J22" s="4">
+        <v>1451821.8792000001</v>
+      </c>
+      <c r="K22" s="4">
+        <v>1451821.8792000001</v>
+      </c>
+      <c r="L22" s="4">
+        <v>1451821.8792000001</v>
+      </c>
       <c r="N22">
         <v>1288535.6162701603</v>
       </c>
       <c r="O22">
-        <v>1288535.6162701603</v>
+        <v>1338535.6159999999</v>
       </c>
       <c r="P22">
-        <v>1288535.6162701603</v>
+        <v>1932803.4240000001</v>
       </c>
       <c r="Q22">
-        <v>1288535.6162701603</v>
+        <v>1932803.4240000001</v>
       </c>
       <c r="R22">
-        <v>1288535.6162701603</v>
-      </c>
-      <c r="S22" s="2"/>
+        <v>1932803.4240000001</v>
+      </c>
       <c r="T22">
-        <v>66660.86</v>
+        <v>185802.14</v>
       </c>
       <c r="U22">
-        <v>66660.86</v>
+        <v>235802.14</v>
       </c>
       <c r="V22">
-        <v>66660.86</v>
+        <v>278703.21000000002</v>
       </c>
       <c r="W22">
-        <v>66660.86</v>
+        <v>278703.21000000002</v>
       </c>
       <c r="X22">
-        <v>66660.86</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>278703.21000000002</v>
+      </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -4842,66 +4580,62 @@
         <v>182187.07860000001</v>
       </c>
       <c r="C23">
-        <v>182187.07860000001</v>
+        <v>232187.07860000001</v>
       </c>
       <c r="D23">
-        <v>182187.07860000001</v>
+        <v>273280.6189</v>
       </c>
       <c r="E23">
-        <v>182187.07860000001</v>
+        <v>273280.6189</v>
       </c>
       <c r="F23">
-        <v>182187.07860000001</v>
-      </c>
-      <c r="G23" s="2"/>
+        <v>273280.6189</v>
+      </c>
       <c r="H23">
         <v>965968.44399999944</v>
       </c>
       <c r="I23">
-        <v>965968.44399999944</v>
-      </c>
-      <c r="J23">
-        <v>965968.44399999944</v>
-      </c>
-      <c r="K23">
-        <v>965968.44399999944</v>
-      </c>
-      <c r="L23">
-        <v>965968.44399999944</v>
-      </c>
-      <c r="M23" s="2"/>
+        <v>1015968.444</v>
+      </c>
+      <c r="J23" s="4">
+        <v>1448952.666</v>
+      </c>
+      <c r="K23" s="4">
+        <v>1448952.666</v>
+      </c>
+      <c r="L23" s="4">
+        <v>1448952.666</v>
+      </c>
       <c r="N23">
         <v>1288662.5713546001</v>
       </c>
       <c r="O23">
-        <v>1288662.5713546001</v>
+        <v>1338662.571</v>
       </c>
       <c r="P23">
-        <v>1288662.5713546001</v>
+        <v>1932993.8565</v>
       </c>
       <c r="Q23">
-        <v>1288662.5713546001</v>
+        <v>1932993.8565</v>
       </c>
       <c r="R23">
-        <v>1288662.5713546001</v>
-      </c>
-      <c r="S23" s="2"/>
+        <v>1932993.8565</v>
+      </c>
       <c r="T23">
-        <v>65659.95</v>
+        <v>182026.51</v>
       </c>
       <c r="U23">
-        <v>65659.95</v>
+        <v>232026.51</v>
       </c>
       <c r="V23">
-        <v>65659.95</v>
+        <v>273039.76500000001</v>
       </c>
       <c r="W23">
-        <v>65659.95</v>
+        <v>273039.76500000001</v>
       </c>
       <c r="X23">
-        <v>65659.95</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>273039.76500000001</v>
+      </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -4911,66 +4645,62 @@
         <v>179454.27239999999</v>
       </c>
       <c r="C24">
-        <v>179454.27239999999</v>
+        <v>229454.27239999999</v>
       </c>
       <c r="D24">
-        <v>179454.27239999999</v>
+        <v>269181.40860000002</v>
       </c>
       <c r="E24">
-        <v>179454.27239999999</v>
+        <v>269181.40860000002</v>
       </c>
       <c r="F24">
-        <v>179454.27239999999</v>
-      </c>
-      <c r="G24" s="2"/>
+        <v>269181.40860000002</v>
+      </c>
       <c r="H24">
         <v>964055.63519999932</v>
       </c>
       <c r="I24">
-        <v>964055.63519999932</v>
-      </c>
-      <c r="J24">
-        <v>964055.63519999932</v>
-      </c>
-      <c r="K24">
-        <v>964055.63519999932</v>
-      </c>
-      <c r="L24">
-        <v>964055.63519999932</v>
-      </c>
-      <c r="M24" s="2"/>
+        <v>1014055.6352</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1446083.4528000001</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1446083.4528000001</v>
+      </c>
+      <c r="L24" s="4">
+        <v>1446083.4528000001</v>
+      </c>
       <c r="N24">
         <v>1288789.5264390404</v>
       </c>
       <c r="O24">
-        <v>1288789.5264390404</v>
+        <v>1338789.5260000001</v>
       </c>
       <c r="P24">
-        <v>1288789.5264390404</v>
+        <v>1933184.2890000001</v>
       </c>
       <c r="Q24">
-        <v>1288789.5264390404</v>
+        <v>1933184.2890000001</v>
       </c>
       <c r="R24">
-        <v>1288789.5264390404</v>
-      </c>
-      <c r="S24" s="2"/>
+        <v>1933184.2890000001</v>
+      </c>
       <c r="T24">
-        <v>64674.05</v>
+        <v>178332.87</v>
       </c>
       <c r="U24">
-        <v>64674.05</v>
+        <v>228332.87</v>
       </c>
       <c r="V24">
-        <v>64674.05</v>
+        <v>267499.30499999999</v>
       </c>
       <c r="W24">
-        <v>64674.05</v>
+        <v>267499.30499999999</v>
       </c>
       <c r="X24">
-        <v>64674.05</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>267499.30499999999</v>
+      </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -4980,66 +4710,62 @@
         <v>176762.4583</v>
       </c>
       <c r="C25">
-        <v>176762.4583</v>
+        <v>226762.4583</v>
       </c>
       <c r="D25">
-        <v>176762.4583</v>
+        <v>265143.68745000003</v>
       </c>
       <c r="E25">
-        <v>176762.4583</v>
+        <v>265143.68745000003</v>
       </c>
       <c r="F25">
-        <v>176762.4583</v>
-      </c>
-      <c r="G25" s="2"/>
+        <v>265143.68745000003</v>
+      </c>
       <c r="H25">
         <v>962142.82639999932</v>
       </c>
       <c r="I25">
-        <v>962142.82639999932</v>
-      </c>
-      <c r="J25">
-        <v>962142.82639999932</v>
-      </c>
-      <c r="K25">
-        <v>962142.82639999932</v>
-      </c>
-      <c r="L25">
-        <v>962142.82639999932</v>
-      </c>
-      <c r="M25" s="2"/>
+        <v>1012142.8264</v>
+      </c>
+      <c r="J25" s="4">
+        <v>1443214.2396</v>
+      </c>
+      <c r="K25" s="4">
+        <v>1443214.2396</v>
+      </c>
+      <c r="L25" s="4">
+        <v>1443214.2396</v>
+      </c>
       <c r="N25">
         <v>1288916.4815234803</v>
       </c>
       <c r="O25">
-        <v>1288916.4815234803</v>
+        <v>1338916.4820000001</v>
       </c>
       <c r="P25">
-        <v>1288916.4815234803</v>
+        <v>1933374.723</v>
       </c>
       <c r="Q25">
-        <v>1288916.4815234803</v>
+        <v>1933374.723</v>
       </c>
       <c r="R25">
-        <v>1288916.4815234803</v>
-      </c>
-      <c r="S25" s="2"/>
+        <v>1933374.723</v>
+      </c>
       <c r="T25">
-        <v>63702.94</v>
+        <v>174720.11</v>
       </c>
       <c r="U25">
-        <v>63702.94</v>
+        <v>224720.11</v>
       </c>
       <c r="V25">
-        <v>63702.94</v>
+        <v>262080.16500000001</v>
       </c>
       <c r="W25">
-        <v>63702.94</v>
+        <v>262080.16500000001</v>
       </c>
       <c r="X25">
-        <v>63702.94</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>262080.16500000001</v>
+      </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -5049,66 +4775,62 @@
         <v>174111.0214</v>
       </c>
       <c r="C26">
-        <v>174111.0214</v>
+        <v>224111.0214</v>
       </c>
       <c r="D26">
-        <v>174111.0214</v>
+        <v>261166.53210000001</v>
       </c>
       <c r="E26">
-        <v>174111.0214</v>
+        <v>261166.53210000001</v>
       </c>
       <c r="F26">
-        <v>174111.0214</v>
-      </c>
-      <c r="G26" s="2"/>
+        <v>261166.53210000001</v>
+      </c>
       <c r="H26">
         <v>960230.01759999921</v>
       </c>
       <c r="I26">
-        <v>960230.01759999921</v>
-      </c>
-      <c r="J26">
-        <v>960230.01759999921</v>
-      </c>
-      <c r="K26">
-        <v>960230.01759999921</v>
-      </c>
-      <c r="L26">
-        <v>960230.01759999921</v>
-      </c>
-      <c r="M26" s="2"/>
+        <v>1010230.0176</v>
+      </c>
+      <c r="J26" s="4">
+        <v>1440345.0264000001</v>
+      </c>
+      <c r="K26" s="4">
+        <v>1440345.0264000001</v>
+      </c>
+      <c r="L26" s="4">
+        <v>1440345.0264000001</v>
+      </c>
       <c r="N26">
         <v>1289043.4366079206</v>
       </c>
       <c r="O26">
-        <v>1289043.4366079206</v>
+        <v>1339043.4369999999</v>
       </c>
       <c r="P26">
-        <v>1289043.4366079206</v>
+        <v>1933565.1555000001</v>
       </c>
       <c r="Q26">
-        <v>1289043.4366079206</v>
+        <v>1933565.1555000001</v>
       </c>
       <c r="R26">
-        <v>1289043.4366079206</v>
-      </c>
-      <c r="S26" s="2"/>
+        <v>1933565.1555000001</v>
+      </c>
       <c r="T26">
-        <v>62746.400000000001</v>
+        <v>171187.17</v>
       </c>
       <c r="U26">
-        <v>62746.400000000001</v>
+        <v>221187.17</v>
       </c>
       <c r="V26">
-        <v>62746.400000000001</v>
+        <v>256780.755</v>
       </c>
       <c r="W26">
-        <v>62746.400000000001</v>
+        <v>256780.755</v>
       </c>
       <c r="X26">
-        <v>62746.400000000001</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>256780.755</v>
+      </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
@@ -5118,73 +4840,73 @@
         <v>171499.3561</v>
       </c>
       <c r="C27">
-        <v>171499.3561</v>
+        <v>221499.3561</v>
       </c>
       <c r="D27">
-        <v>171499.3561</v>
+        <v>257249.03414999999</v>
       </c>
       <c r="E27">
-        <v>171499.3561</v>
+        <v>257249.03414999999</v>
       </c>
       <c r="F27">
-        <v>171499.3561</v>
+        <v>257249.03414999999</v>
       </c>
       <c r="G27">
-        <v>171499.3561</v>
+        <v>257249.03414999999</v>
       </c>
       <c r="H27">
         <v>958317.20879999921</v>
       </c>
       <c r="I27">
-        <v>958317.20879999921</v>
-      </c>
-      <c r="J27">
-        <v>958317.20879999921</v>
-      </c>
-      <c r="K27">
-        <v>958317.20879999921</v>
-      </c>
-      <c r="L27">
-        <v>958317.20879999921</v>
-      </c>
-      <c r="M27">
-        <v>958317.20879999921</v>
+        <v>1008317.2088</v>
+      </c>
+      <c r="J27" s="4">
+        <v>1437475.8132</v>
+      </c>
+      <c r="K27" s="4">
+        <v>1437475.8132</v>
+      </c>
+      <c r="L27" s="4">
+        <v>1437475.8132</v>
+      </c>
+      <c r="M27" s="4">
+        <v>1437475.8132</v>
       </c>
       <c r="N27">
         <v>1289170.3916923604</v>
       </c>
       <c r="O27">
-        <v>1289170.3916923604</v>
+        <v>1339170.392</v>
       </c>
       <c r="P27">
-        <v>1289170.3916923604</v>
+        <v>1933755.588</v>
       </c>
       <c r="Q27">
-        <v>1289170.3916923604</v>
+        <v>1933755.588</v>
       </c>
       <c r="R27">
-        <v>1289170.3916923604</v>
+        <v>1933755.588</v>
       </c>
       <c r="S27">
-        <v>1289170.3916923604</v>
+        <v>1933755.588</v>
       </c>
       <c r="T27">
-        <v>61804.2</v>
+        <v>167732.98000000001</v>
       </c>
       <c r="U27">
-        <v>61804.2</v>
+        <v>217732.98</v>
       </c>
       <c r="V27">
-        <v>61804.2</v>
+        <v>251599.47</v>
       </c>
       <c r="W27">
-        <v>61804.2</v>
+        <v>251599.47</v>
       </c>
       <c r="X27">
-        <v>61804.2</v>
+        <v>251599.47</v>
       </c>
       <c r="Y27">
-        <v>61804.2</v>
+        <v>251599.47</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
@@ -5195,73 +4917,73 @@
         <v>168926.8658</v>
       </c>
       <c r="C28">
-        <v>168926.8658</v>
+        <v>218926.8658</v>
       </c>
       <c r="D28">
-        <v>168926.8658</v>
+        <v>253390.29870000001</v>
       </c>
       <c r="E28">
-        <v>168926.8658</v>
+        <v>253390.29870000001</v>
       </c>
       <c r="F28">
-        <v>168926.8658</v>
+        <v>253390.29870000001</v>
       </c>
       <c r="G28">
-        <v>168926.8658</v>
+        <v>253390.29870000001</v>
       </c>
       <c r="H28">
         <v>956404.40000000026</v>
       </c>
       <c r="I28">
-        <v>956404.40000000026</v>
-      </c>
-      <c r="J28">
-        <v>956404.40000000026</v>
-      </c>
-      <c r="K28">
-        <v>956404.40000000026</v>
-      </c>
-      <c r="L28">
-        <v>956404.40000000026</v>
-      </c>
-      <c r="M28">
-        <v>956404.40000000026</v>
+        <v>1006404.4</v>
+      </c>
+      <c r="J28" s="4">
+        <v>1434606.6</v>
+      </c>
+      <c r="K28" s="4">
+        <v>1434606.6</v>
+      </c>
+      <c r="L28" s="4">
+        <v>1434606.6</v>
+      </c>
+      <c r="M28" s="4">
+        <v>1434606.6</v>
       </c>
       <c r="N28">
         <v>1289297.3467768</v>
       </c>
       <c r="O28">
-        <v>1289297.3467768</v>
+        <v>1339297.3470000001</v>
       </c>
       <c r="P28">
-        <v>1289297.3467768</v>
+        <v>1933946.0205000001</v>
       </c>
       <c r="Q28">
-        <v>1289297.3467768</v>
+        <v>1933946.0205000001</v>
       </c>
       <c r="R28">
-        <v>1289297.3467768</v>
+        <v>1933946.0205000001</v>
       </c>
       <c r="S28">
-        <v>1289297.3467768</v>
+        <v>1933946.0205000001</v>
       </c>
       <c r="T28">
-        <v>60876.14</v>
+        <v>164356.51999999999</v>
       </c>
       <c r="U28">
-        <v>60876.14</v>
+        <v>214356.52</v>
       </c>
       <c r="V28">
-        <v>60876.14</v>
+        <v>246534.78</v>
       </c>
       <c r="W28">
-        <v>60876.14</v>
+        <v>246534.78</v>
       </c>
       <c r="X28">
-        <v>60876.14</v>
+        <v>246534.78</v>
       </c>
       <c r="Y28">
-        <v>60876.14</v>
+        <v>246534.78</v>
       </c>
     </row>
   </sheetData>
@@ -5278,79 +5000,79 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="3" t="s">
         <v>67</v>
       </c>
     </row>
@@ -5361,35 +5083,15 @@
       <c r="B2">
         <v>303600</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2">
         <v>1673707.7</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
       <c r="N2">
         <v>2337972.5216000001</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="3">
-        <v>129380</v>
-      </c>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
+      <c r="T2">
+        <v>527469.86</v>
+      </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -5398,35 +5100,15 @@
       <c r="B3">
         <v>299045.40000000002</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
       <c r="H3">
         <v>1660955.6413333334</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
       <c r="N3">
         <v>2318026.381866667</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="3">
-        <v>127438.3</v>
-      </c>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
+      <c r="T3">
+        <v>516785.56</v>
+      </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -5435,35 +5117,15 @@
       <c r="B4">
         <v>294559.71899999998</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
       <c r="H4">
         <v>1648203.5826666667</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
       <c r="N4">
         <v>2298080.2421333333</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="3">
-        <v>125526.73</v>
-      </c>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
+      <c r="T4">
+        <v>506302.5</v>
+      </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -5472,35 +5134,15 @@
       <c r="B5">
         <v>290141.32319999998</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
       <c r="H5">
         <v>1635451.524</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
       <c r="N5">
         <v>2278134.1023999997</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="3">
-        <v>123644.83</v>
-      </c>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
+      <c r="T5">
+        <v>496017.89</v>
+      </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -5509,35 +5151,15 @@
       <c r="B6">
         <v>285788.2034</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
       <c r="H6">
         <v>1622699.4653333335</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
       <c r="N6">
         <v>2258187.9626666661</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="3">
-        <v>121792.16</v>
-      </c>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
+      <c r="T6">
+        <v>485929.01</v>
+      </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -5549,40 +5171,24 @@
       <c r="C7">
         <v>281498.4804</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
       <c r="H7">
         <v>1609947.4066666667</v>
       </c>
       <c r="I7">
         <v>1609947.4066666667</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
       <c r="N7">
         <v>2238241.8229333302</v>
       </c>
       <c r="O7">
         <v>2238241.8229333302</v>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="3">
-        <v>119968.28</v>
-      </c>
-      <c r="U7" s="3">
-        <v>119968.28</v>
-      </c>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
+      <c r="T7">
+        <v>476033.18</v>
+      </c>
+      <c r="U7">
+        <v>476033.18</v>
+      </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -5592,42 +5198,26 @@
         <v>277270.34419999999</v>
       </c>
       <c r="C8">
-        <v>277270.34419999999</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+        <v>207952.75815000001</v>
+      </c>
       <c r="H8">
         <v>1597195.3480000002</v>
       </c>
       <c r="I8">
-        <v>1597195.3480000002</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+        <v>1197896.5109999999</v>
+      </c>
       <c r="N8">
         <v>2218295.6831999999</v>
       </c>
       <c r="O8">
-        <v>2218295.6831999999</v>
-      </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="3">
-        <v>118172.75</v>
-      </c>
-      <c r="U8" s="3">
-        <v>118172.75</v>
-      </c>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
+        <v>1663721.7622499999</v>
+      </c>
+      <c r="T8">
+        <v>466327.8</v>
+      </c>
+      <c r="U8">
+        <v>349745.85</v>
+      </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -5637,42 +5227,26 @@
         <v>273102.28909999999</v>
       </c>
       <c r="C9">
-        <v>273102.28909999999</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+        <v>204826.71682500001</v>
+      </c>
       <c r="H9">
         <v>1594326.1348000003</v>
       </c>
       <c r="I9">
-        <v>1594326.1348000003</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+        <v>1195744.6012500001</v>
+      </c>
       <c r="N9">
         <v>2205259.4561600001</v>
       </c>
       <c r="O9">
-        <v>2205259.4561600001</v>
-      </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="3">
-        <v>116405.16</v>
-      </c>
-      <c r="U9" s="3">
-        <v>116405.16</v>
-      </c>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
+        <v>1653944.5919999999</v>
+      </c>
+      <c r="T9">
+        <v>456810.3</v>
+      </c>
+      <c r="U9">
+        <v>342607.72499999998</v>
+      </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -5682,42 +5256,26 @@
         <v>268993.2548</v>
       </c>
       <c r="C10">
-        <v>268993.2548</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+        <v>201744.9411</v>
+      </c>
       <c r="H10">
         <v>1591456.9216000002</v>
       </c>
       <c r="I10">
-        <v>1591456.9216000002</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+        <v>1193592.6915</v>
+      </c>
       <c r="N10">
         <v>2192223.2291199998</v>
       </c>
       <c r="O10">
-        <v>2192223.2291199998</v>
-      </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="3">
-        <v>114665.09</v>
-      </c>
-      <c r="U10" s="3">
-        <v>114665.09</v>
-      </c>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
+        <v>1644167.42175</v>
+      </c>
+      <c r="T10">
+        <v>447478.16</v>
+      </c>
+      <c r="U10">
+        <v>335608.62</v>
+      </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -5727,42 +5285,26 @@
         <v>264942.41499999998</v>
       </c>
       <c r="C11">
-        <v>264942.41499999998</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+        <v>198706.81125</v>
+      </c>
       <c r="H11">
         <v>1588587.7084000004</v>
       </c>
       <c r="I11">
-        <v>1588587.7084000004</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+        <v>1191440.781</v>
+      </c>
       <c r="N11">
         <v>2179187.0020799995</v>
       </c>
       <c r="O11">
-        <v>2179187.0020799995</v>
-      </c>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="3">
-        <v>112952.12</v>
-      </c>
-      <c r="U11" s="3">
-        <v>112952.12</v>
-      </c>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
+        <v>1634390.2515</v>
+      </c>
+      <c r="T11">
+        <v>438328.91</v>
+      </c>
+      <c r="U11">
+        <v>328746.6825</v>
+      </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -5772,50 +5314,38 @@
         <v>260948.7948</v>
       </c>
       <c r="C12">
-        <v>260948.7948</v>
+        <v>195711.5961</v>
       </c>
       <c r="D12">
-        <v>260948.7948</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+        <v>195711.5961</v>
+      </c>
       <c r="H12">
         <v>1585718.4952000002</v>
       </c>
       <c r="I12">
-        <v>1585718.4952000002</v>
+        <v>1189288.87075</v>
       </c>
       <c r="J12">
-        <v>1585718.4952000002</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+        <v>1189288.87075</v>
+      </c>
       <c r="N12">
         <v>2166150.7750399997</v>
       </c>
       <c r="O12">
-        <v>2166150.7750399997</v>
+        <v>1624613.08125</v>
       </c>
       <c r="P12">
-        <v>2166150.7750399997</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="3">
-        <v>111265.84</v>
-      </c>
-      <c r="U12" s="3">
-        <v>111265.84</v>
-      </c>
-      <c r="V12" s="3">
-        <v>111265.84</v>
-      </c>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
+        <v>1624613.08125</v>
+      </c>
+      <c r="T12">
+        <v>429360.14</v>
+      </c>
+      <c r="U12">
+        <v>322020.10499999998</v>
+      </c>
+      <c r="V12">
+        <v>322020.10499999998</v>
+      </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -5825,50 +5355,38 @@
         <v>257011.4613</v>
       </c>
       <c r="C13">
-        <v>257011.4613</v>
+        <v>192758.595975</v>
       </c>
       <c r="D13">
-        <v>257011.4613</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+        <v>289137.89399999997</v>
+      </c>
       <c r="H13">
         <v>1582849.2820000004</v>
       </c>
       <c r="I13">
-        <v>1582849.2820000004</v>
+        <v>1187136.9605</v>
       </c>
       <c r="J13">
-        <v>1582849.2820000004</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+        <v>1780705.4415</v>
+      </c>
       <c r="N13">
         <v>2153114.5479999995</v>
       </c>
       <c r="O13">
-        <v>2153114.5479999995</v>
+        <v>1614835.9110000001</v>
       </c>
       <c r="P13">
-        <v>2153114.5479999995</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="3">
-        <v>109605.86</v>
-      </c>
-      <c r="U13" s="3">
-        <v>109605.86</v>
-      </c>
-      <c r="V13" s="3">
-        <v>109605.86</v>
-      </c>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
+        <v>2422253.8665</v>
+      </c>
+      <c r="T13">
+        <v>420569.49</v>
+      </c>
+      <c r="U13">
+        <v>473140.67625000002</v>
+      </c>
+      <c r="V13">
+        <v>709711.01445000002</v>
+      </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -5878,50 +5396,38 @@
         <v>253129.39139999999</v>
       </c>
       <c r="C14">
-        <v>253129.39139999999</v>
+        <v>189847.04355</v>
       </c>
       <c r="D14">
-        <v>253129.39139999999</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+        <v>284770.56540000002</v>
+      </c>
       <c r="H14">
         <v>1579980.0688000005</v>
       </c>
       <c r="I14">
-        <v>1579980.0688000005</v>
+        <v>1184985.0507499999</v>
       </c>
       <c r="J14">
-        <v>1579980.0688000005</v>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+        <v>1777477.5765</v>
+      </c>
       <c r="N14">
         <v>2140078.3209599997</v>
       </c>
       <c r="O14">
-        <v>2140078.3209599997</v>
+        <v>1605058.7407500001</v>
       </c>
       <c r="P14">
-        <v>2140078.3209599997</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="3">
-        <v>107971.77</v>
-      </c>
-      <c r="U14" s="3">
-        <v>107971.77</v>
-      </c>
-      <c r="V14" s="3">
-        <v>107971.77</v>
-      </c>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
+        <v>2407588.1115000001</v>
+      </c>
+      <c r="T14">
+        <v>411954.65</v>
+      </c>
+      <c r="U14">
+        <v>463450.48125000001</v>
+      </c>
+      <c r="V14">
+        <v>695175.72195000004</v>
+      </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -5931,50 +5437,38 @@
         <v>249301.63759999999</v>
       </c>
       <c r="C15">
-        <v>249301.63759999999</v>
+        <v>186976.22820000001</v>
       </c>
       <c r="D15">
-        <v>249301.63759999999</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+        <v>280464.34230000002</v>
+      </c>
       <c r="H15">
         <v>1577110.8556000004</v>
       </c>
       <c r="I15">
-        <v>1577110.8556000004</v>
+        <v>1182833.14075</v>
       </c>
       <c r="J15">
-        <v>1577110.8556000004</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+        <v>1774250.7115</v>
+      </c>
       <c r="N15">
         <v>2127042.0939199994</v>
       </c>
       <c r="O15">
-        <v>2127042.0939199994</v>
+        <v>1595281.5704999999</v>
       </c>
       <c r="P15">
-        <v>2127042.0939199994</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+        <v>2392922.3565000002</v>
+      </c>
       <c r="T15">
-        <v>106363.2</v>
+        <v>403513.36</v>
       </c>
       <c r="U15">
-        <v>106363.2</v>
+        <v>453952.53</v>
       </c>
       <c r="V15">
-        <v>106363.2</v>
-      </c>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
+        <v>680928.79500000004</v>
+      </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -5984,50 +5478,38 @@
         <v>245527.30809999999</v>
       </c>
       <c r="C16">
-        <v>245527.30809999999</v>
+        <v>184145.48107499999</v>
       </c>
       <c r="D16">
-        <v>245527.30809999999</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+        <v>276218.22169999999</v>
+      </c>
       <c r="H16">
         <v>1574241.6424000005</v>
       </c>
       <c r="I16">
-        <v>1574241.6424000005</v>
+        <v>1180681.2315</v>
       </c>
       <c r="J16">
-        <v>1574241.6424000005</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+        <v>1771023.848</v>
+      </c>
       <c r="N16">
         <v>2114005.8668799992</v>
       </c>
       <c r="O16">
-        <v>2114005.8668799992</v>
+        <v>1585504.4002499999</v>
       </c>
       <c r="P16">
-        <v>2114005.8668799992</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
+        <v>2378256.6</v>
+      </c>
       <c r="T16">
-        <v>104779.75</v>
+        <v>395243.39</v>
       </c>
       <c r="U16">
-        <v>104779.75</v>
+        <v>444648.81374999997</v>
       </c>
       <c r="V16">
-        <v>104779.75</v>
-      </c>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
+        <v>666973.22069999995</v>
+      </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -6037,58 +5519,50 @@
         <v>241805.39859999999</v>
       </c>
       <c r="C17">
-        <v>241805.39859999999</v>
+        <v>181354.04934999999</v>
       </c>
       <c r="D17">
-        <v>241805.39859999999</v>
+        <v>272031.07410000003</v>
       </c>
       <c r="E17">
-        <v>241805.39859999999</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+        <v>272031.07410000003</v>
+      </c>
       <c r="H17">
         <v>1571372.4292000004</v>
       </c>
       <c r="I17">
-        <v>1571372.4292000004</v>
+        <v>1178529.3217499999</v>
       </c>
       <c r="J17">
-        <v>1571372.4292000004</v>
+        <v>1767796.983</v>
       </c>
       <c r="K17">
-        <v>1571372.4292000004</v>
-      </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+        <v>1767796.983</v>
+      </c>
       <c r="N17">
         <v>2100969.6398399994</v>
       </c>
       <c r="O17">
-        <v>2100969.6398399994</v>
+        <v>1575727.23</v>
       </c>
       <c r="P17">
-        <v>2100969.6398399994</v>
+        <v>2363590.8450000002</v>
       </c>
       <c r="Q17">
-        <v>2100969.6398399994</v>
-      </c>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
+        <v>2363590.8450000002</v>
+      </c>
       <c r="T17">
-        <v>103221.06</v>
+        <v>387142.59</v>
       </c>
       <c r="U17">
-        <v>103221.06</v>
+        <v>435535.41375000001</v>
       </c>
       <c r="V17">
-        <v>103221.06</v>
+        <v>653303.12069999997</v>
       </c>
       <c r="W17">
-        <v>103221.06</v>
-      </c>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
+        <v>653303.12069999997</v>
+      </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -6098,58 +5572,50 @@
         <v>238134.9901</v>
       </c>
       <c r="C18">
-        <v>238134.9901</v>
+        <v>178601.24257500001</v>
       </c>
       <c r="D18">
-        <v>238134.9901</v>
+        <v>267901.864</v>
       </c>
       <c r="E18">
-        <v>238134.9901</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+        <v>267901.864</v>
+      </c>
       <c r="H18">
         <v>1568503.2160000005</v>
       </c>
       <c r="I18">
-        <v>1568503.2160000005</v>
+        <v>1176377.412</v>
       </c>
       <c r="J18">
-        <v>1568503.2160000005</v>
+        <v>1764570.118</v>
       </c>
       <c r="K18">
-        <v>1568503.2160000005</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+        <v>1764570.118</v>
+      </c>
       <c r="N18">
         <v>2087933.4128</v>
       </c>
       <c r="O18">
-        <v>2087933.4128</v>
+        <v>1565949.05975</v>
       </c>
       <c r="P18">
-        <v>2087933.4128</v>
+        <v>2348925.09</v>
       </c>
       <c r="Q18">
-        <v>2087933.4128</v>
-      </c>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
+        <v>2348925.09</v>
+      </c>
       <c r="T18">
-        <v>101686.74</v>
+        <v>379208.83</v>
       </c>
       <c r="U18">
-        <v>101686.74</v>
+        <v>426609.93375000003</v>
       </c>
       <c r="V18">
-        <v>101686.74</v>
+        <v>639914.9007</v>
       </c>
       <c r="W18">
-        <v>101686.74</v>
-      </c>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
+        <v>639914.9007</v>
+      </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -6159,58 +5625,50 @@
         <v>234515.065</v>
       </c>
       <c r="C19">
-        <v>234515.065</v>
+        <v>175886.29874999999</v>
       </c>
       <c r="D19">
-        <v>234515.065</v>
+        <v>263829.44819999998</v>
       </c>
       <c r="E19">
-        <v>234515.065</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+        <v>263829.44819999998</v>
+      </c>
       <c r="H19">
         <v>1565634.0028000006</v>
       </c>
       <c r="I19">
-        <v>1565634.0028000006</v>
+        <v>1174225.5022499999</v>
       </c>
       <c r="J19">
-        <v>1565634.0028000006</v>
+        <v>1761343.253</v>
       </c>
       <c r="K19">
-        <v>1565634.0028000006</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+        <v>1761343.253</v>
+      </c>
       <c r="N19">
         <v>2076927.41784</v>
       </c>
       <c r="O19">
-        <v>2076927.41784</v>
+        <v>1557695.5634999999</v>
       </c>
       <c r="P19">
-        <v>2076927.41784</v>
+        <v>2336543.3459999999</v>
       </c>
       <c r="Q19">
-        <v>2076927.41784</v>
-      </c>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
+        <v>2336543.3459999999</v>
+      </c>
       <c r="T19">
-        <v>100176.44</v>
+        <v>371440.05</v>
       </c>
       <c r="U19">
-        <v>100176.44</v>
+        <v>417868.55625000002</v>
       </c>
       <c r="V19">
-        <v>100176.44</v>
+        <v>626802.83444999997</v>
       </c>
       <c r="W19">
-        <v>100176.44</v>
-      </c>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
+        <v>626802.83444999997</v>
+      </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -6220,58 +5678,50 @@
         <v>230944.68799999999</v>
       </c>
       <c r="C20">
-        <v>230944.68799999999</v>
+        <v>173208.516</v>
       </c>
       <c r="D20">
-        <v>230944.68799999999</v>
+        <v>259812.774</v>
       </c>
       <c r="E20">
-        <v>230944.68799999999</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+        <v>259812.774</v>
+      </c>
       <c r="H20">
         <v>1562764.7896000005</v>
       </c>
       <c r="I20">
-        <v>1562764.7896000005</v>
+        <v>1172073.5925</v>
       </c>
       <c r="J20">
-        <v>1562764.7896000005</v>
+        <v>1758116.3895</v>
       </c>
       <c r="K20">
-        <v>1562764.7896000005</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+        <v>1758116.3895</v>
+      </c>
       <c r="N20">
         <v>2065921.4228800002</v>
       </c>
       <c r="O20">
-        <v>2065921.4228800002</v>
+        <v>1549442.0672500001</v>
       </c>
       <c r="P20">
-        <v>2065921.4228800002</v>
+        <v>2324163.1005000002</v>
       </c>
       <c r="Q20">
-        <v>2065921.4228800002</v>
-      </c>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
+        <v>2324163.1005000002</v>
+      </c>
       <c r="T20">
-        <v>98689.79</v>
+        <v>363834.24</v>
       </c>
       <c r="U20">
-        <v>98689.79</v>
+        <v>409307.52</v>
       </c>
       <c r="V20">
-        <v>98689.79</v>
+        <v>613961.28</v>
       </c>
       <c r="W20">
-        <v>98689.79</v>
-      </c>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
+        <v>613961.28</v>
+      </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -6281,58 +5731,50 @@
         <v>227422.96530000001</v>
       </c>
       <c r="C21">
-        <v>227422.96530000001</v>
+        <v>170567.223975</v>
       </c>
       <c r="D21">
-        <v>227422.96530000001</v>
+        <v>255850.83600000001</v>
       </c>
       <c r="E21">
-        <v>227422.96530000001</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+        <v>255850.83600000001</v>
+      </c>
       <c r="H21">
         <v>1559895.5764000006</v>
       </c>
       <c r="I21">
-        <v>1559895.5764000006</v>
+        <v>1169921.682</v>
       </c>
       <c r="J21">
-        <v>1559895.5764000006</v>
+        <v>1754889.523</v>
       </c>
       <c r="K21">
-        <v>1559895.5764000006</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+        <v>1754889.523</v>
+      </c>
       <c r="N21">
         <v>2054915.4279200002</v>
       </c>
       <c r="O21">
-        <v>2054915.4279200002</v>
+        <v>1541188.571</v>
       </c>
       <c r="P21">
-        <v>2054915.4279200002</v>
+        <v>2311782.8565000002</v>
       </c>
       <c r="Q21">
-        <v>2054915.4279200002</v>
-      </c>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
+        <v>2311782.8565000002</v>
+      </c>
       <c r="T21">
-        <v>97226.44</v>
+        <v>356389.41</v>
       </c>
       <c r="U21">
-        <v>97226.44</v>
+        <v>400923.08624999999</v>
       </c>
       <c r="V21">
-        <v>97226.44</v>
+        <v>601384.62945000001</v>
       </c>
       <c r="W21">
-        <v>97226.44</v>
-      </c>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
+        <v>601384.62945000001</v>
+      </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -6342,66 +5784,62 @@
         <v>223948.88099999999</v>
       </c>
       <c r="C22">
-        <v>223948.88099999999</v>
+        <v>167961.66075000001</v>
       </c>
       <c r="D22">
-        <v>223948.88099999999</v>
+        <v>251942.49119999999</v>
       </c>
       <c r="E22">
-        <v>223948.88099999999</v>
+        <v>251942.49119999999</v>
       </c>
       <c r="F22">
-        <v>223948.88099999999</v>
-      </c>
-      <c r="G22" s="2"/>
+        <v>251942.49119999999</v>
+      </c>
       <c r="H22">
         <v>1557026.3632000005</v>
       </c>
       <c r="I22">
-        <v>1557026.3632000005</v>
+        <v>1167769.7722499999</v>
       </c>
       <c r="J22">
-        <v>1557026.3632000005</v>
+        <v>1751662.6580000001</v>
       </c>
       <c r="K22">
-        <v>1557026.3632000005</v>
+        <v>1751662.6580000001</v>
       </c>
       <c r="L22">
-        <v>1557026.3632000005</v>
-      </c>
-      <c r="M22" s="2"/>
+        <v>1751662.6580000001</v>
+      </c>
       <c r="N22">
         <v>2043909.4329600004</v>
       </c>
       <c r="O22">
-        <v>2043909.4329600004</v>
+        <v>1532935.0747499999</v>
       </c>
       <c r="P22">
-        <v>2043909.4329600004</v>
+        <v>2299402.6124999998</v>
       </c>
       <c r="Q22">
-        <v>2043909.4329600004</v>
+        <v>2299402.6124999998</v>
       </c>
       <c r="R22">
-        <v>2043909.4329600004</v>
-      </c>
-      <c r="S22" s="2"/>
+        <v>2299402.6124999998</v>
+      </c>
       <c r="T22">
-        <v>95786.05</v>
+        <v>349103.66</v>
       </c>
       <c r="U22">
-        <v>95786.05</v>
+        <v>392711.61749999999</v>
       </c>
       <c r="V22">
-        <v>95786.05</v>
+        <v>589067.42625000002</v>
       </c>
       <c r="W22">
-        <v>95786.05</v>
+        <v>589067.42625000002</v>
       </c>
       <c r="X22">
-        <v>95786.05</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>589067.42625000002</v>
+      </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -6411,66 +5849,62 @@
         <v>220521.46350000001</v>
       </c>
       <c r="C23">
-        <v>220521.46350000001</v>
+        <v>165391.09770000001</v>
       </c>
       <c r="D23">
-        <v>220521.46350000001</v>
+        <v>248086.64655</v>
       </c>
       <c r="E23">
-        <v>220521.46350000001</v>
+        <v>248086.64655</v>
       </c>
       <c r="F23">
-        <v>220521.46350000001</v>
-      </c>
-      <c r="G23" s="2"/>
+        <v>248086.64655</v>
+      </c>
       <c r="H23">
         <v>1554157.1500000006</v>
       </c>
       <c r="I23">
-        <v>1554157.1500000006</v>
+        <v>1165617.8625</v>
       </c>
       <c r="J23">
-        <v>1554157.1500000006</v>
+        <v>1748435.7945000001</v>
       </c>
       <c r="K23">
-        <v>1554157.1500000006</v>
+        <v>1748435.7945000001</v>
       </c>
       <c r="L23">
-        <v>1554157.1500000006</v>
-      </c>
-      <c r="M23" s="2"/>
+        <v>1748435.7945000001</v>
+      </c>
       <c r="N23">
         <v>2032903.4380000005</v>
       </c>
       <c r="O23">
-        <v>2032903.4380000005</v>
+        <v>1524681.5785000001</v>
       </c>
       <c r="P23">
-        <v>2032903.4380000005</v>
+        <v>2287022.3684999999</v>
       </c>
       <c r="Q23">
-        <v>2032903.4380000005</v>
+        <v>2287022.3684999999</v>
       </c>
       <c r="R23">
-        <v>2032903.4380000005</v>
-      </c>
-      <c r="S23" s="2"/>
+        <v>2287022.3684999999</v>
+      </c>
       <c r="T23">
-        <v>94368.26</v>
+        <v>341975.1</v>
       </c>
       <c r="U23">
-        <v>94368.26</v>
+        <v>384669.48749999999</v>
       </c>
       <c r="V23">
-        <v>94368.26</v>
+        <v>577004.23124999995</v>
       </c>
       <c r="W23">
-        <v>94368.26</v>
+        <v>577004.23124999995</v>
       </c>
       <c r="X23">
-        <v>94368.26</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>577004.23124999995</v>
+      </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -6480,66 +5914,62 @@
         <v>217139.74350000001</v>
       </c>
       <c r="C24">
-        <v>217139.74350000001</v>
+        <v>162854.80762499999</v>
       </c>
       <c r="D24">
-        <v>217139.74350000001</v>
+        <v>244282.2114</v>
       </c>
       <c r="E24">
-        <v>217139.74350000001</v>
+        <v>244282.2114</v>
       </c>
       <c r="F24">
-        <v>217139.74350000001</v>
-      </c>
-      <c r="G24" s="2"/>
+        <v>244282.2114</v>
+      </c>
       <c r="H24">
         <v>1551287.9368000007</v>
       </c>
       <c r="I24">
-        <v>1551287.9368000007</v>
+        <v>1163465.9527499999</v>
       </c>
       <c r="J24">
-        <v>1551287.9368000007</v>
+        <v>1745208.9295000001</v>
       </c>
       <c r="K24">
-        <v>1551287.9368000007</v>
+        <v>1745208.9295000001</v>
       </c>
       <c r="L24">
-        <v>1551287.9368000007</v>
-      </c>
-      <c r="M24" s="2"/>
+        <v>1745208.9295000001</v>
+      </c>
       <c r="N24">
         <v>2021897.4430400007</v>
       </c>
       <c r="O24">
-        <v>2021897.4430400007</v>
+        <v>1516428.08225</v>
       </c>
       <c r="P24">
-        <v>2021897.4430400007</v>
+        <v>2274642.1230000001</v>
       </c>
       <c r="Q24">
-        <v>2021897.4430400007</v>
+        <v>2274642.1230000001</v>
       </c>
       <c r="R24">
-        <v>2021897.4430400007</v>
-      </c>
-      <c r="S24" s="2"/>
+        <v>2274642.1230000001</v>
+      </c>
       <c r="T24">
-        <v>92972.74</v>
+        <v>334991.90000000002</v>
       </c>
       <c r="U24">
-        <v>92972.74</v>
+        <v>376793.88750000001</v>
       </c>
       <c r="V24">
-        <v>92972.74</v>
+        <v>565190.83125000005</v>
       </c>
       <c r="W24">
-        <v>92972.74</v>
+        <v>565190.83125000005</v>
       </c>
       <c r="X24">
-        <v>92972.74</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>565190.83125000005</v>
+      </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -6549,66 +5979,62 @@
         <v>213802.75769999999</v>
       </c>
       <c r="C25">
-        <v>213802.75769999999</v>
+        <v>160352.06817499999</v>
       </c>
       <c r="D25">
-        <v>213802.75769999999</v>
+        <v>240528.1023</v>
       </c>
       <c r="E25">
-        <v>213802.75769999999</v>
+        <v>240528.1023</v>
       </c>
       <c r="F25">
-        <v>213802.75769999999</v>
-      </c>
-      <c r="G25" s="2"/>
+        <v>240528.1023</v>
+      </c>
       <c r="H25">
         <v>1548418.7236000006</v>
       </c>
       <c r="I25">
-        <v>1548418.7236000006</v>
+        <v>1161314.0430000001</v>
       </c>
       <c r="J25">
-        <v>1548418.7236000006</v>
+        <v>1741982.0645000001</v>
       </c>
       <c r="K25">
-        <v>1548418.7236000006</v>
+        <v>1741982.0645000001</v>
       </c>
       <c r="L25">
-        <v>1548418.7236000006</v>
-      </c>
-      <c r="M25" s="2"/>
+        <v>1741982.0645000001</v>
+      </c>
       <c r="N25">
         <v>2010891.4480800009</v>
       </c>
       <c r="O25">
-        <v>2010891.4480800009</v>
+        <v>1508174.5859999999</v>
       </c>
       <c r="P25">
-        <v>2010891.4480800009</v>
+        <v>2262261.8790000002</v>
       </c>
       <c r="Q25">
-        <v>2010891.4480800009</v>
+        <v>2262261.8790000002</v>
       </c>
       <c r="R25">
-        <v>2010891.4480800009</v>
-      </c>
-      <c r="S25" s="2"/>
+        <v>2262261.8790000002</v>
+      </c>
       <c r="T25">
-        <v>91599.15</v>
+        <v>328152.28999999998</v>
       </c>
       <c r="U25">
-        <v>91599.15</v>
+        <v>369081.32624999998</v>
       </c>
       <c r="V25">
-        <v>91599.15</v>
+        <v>553621.98944999999</v>
       </c>
       <c r="W25">
-        <v>91599.15</v>
+        <v>553621.98944999999</v>
       </c>
       <c r="X25">
-        <v>91599.15</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>553621.98944999999</v>
+      </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -6618,66 +6044,62 @@
         <v>210509.61679999999</v>
       </c>
       <c r="C26">
-        <v>210509.61679999999</v>
+        <v>157882.2126</v>
       </c>
       <c r="D26">
-        <v>210509.61679999999</v>
+        <v>236823.31899999999</v>
       </c>
       <c r="E26">
-        <v>210509.61679999999</v>
+        <v>236823.31899999999</v>
       </c>
       <c r="F26">
-        <v>210509.61679999999</v>
-      </c>
-      <c r="G26" s="2"/>
+        <v>236823.31899999999</v>
+      </c>
       <c r="H26">
         <v>1545549.5104000007</v>
       </c>
       <c r="I26">
-        <v>1545549.5104000007</v>
+        <v>1159162.1329999999</v>
       </c>
       <c r="J26">
-        <v>1545549.5104000007</v>
+        <v>1738755.1995000001</v>
       </c>
       <c r="K26">
-        <v>1545549.5104000007</v>
+        <v>1738755.1995000001</v>
       </c>
       <c r="L26">
-        <v>1545549.5104000007</v>
-      </c>
-      <c r="M26" s="2"/>
+        <v>1738755.1995000001</v>
+      </c>
       <c r="N26">
         <v>1999885.4531200009</v>
       </c>
       <c r="O26">
-        <v>1999885.4531200009</v>
+        <v>1499921.08975</v>
       </c>
       <c r="P26">
-        <v>1999885.4531200009</v>
+        <v>2249881.6349999998</v>
       </c>
       <c r="Q26">
-        <v>1999885.4531200009</v>
+        <v>2249881.6349999998</v>
       </c>
       <c r="R26">
-        <v>1999885.4531200009</v>
-      </c>
-      <c r="S26" s="2"/>
+        <v>2249881.6349999998</v>
+      </c>
       <c r="T26">
-        <v>90247.16</v>
+        <v>321454.53999999998</v>
       </c>
       <c r="U26">
-        <v>90247.16</v>
+        <v>361528.65749999997</v>
       </c>
       <c r="V26">
-        <v>90247.16</v>
+        <v>542292.98624999996</v>
       </c>
       <c r="W26">
-        <v>90247.16</v>
+        <v>542292.98624999996</v>
       </c>
       <c r="X26">
-        <v>90247.16</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>542292.98624999996</v>
+      </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
@@ -6687,73 +6109,73 @@
         <v>207259.3126</v>
       </c>
       <c r="C27">
-        <v>207259.3126</v>
+        <v>155444.48444999999</v>
       </c>
       <c r="D27">
-        <v>207259.3126</v>
+        <v>233166.72675</v>
       </c>
       <c r="E27">
-        <v>207259.3126</v>
+        <v>233166.72675</v>
       </c>
       <c r="F27">
-        <v>207259.3126</v>
+        <v>233166.72675</v>
       </c>
       <c r="G27">
-        <v>207259.3126</v>
+        <v>233166.72675</v>
       </c>
       <c r="H27">
         <v>1542680.2972000006</v>
       </c>
       <c r="I27">
-        <v>1542680.2972000006</v>
+        <v>1157010.223</v>
       </c>
       <c r="J27">
-        <v>1542680.2972000006</v>
+        <v>1735528.3345000001</v>
       </c>
       <c r="K27">
-        <v>1542680.2972000006</v>
+        <v>1735528.3345000001</v>
       </c>
       <c r="L27">
-        <v>1542680.2972000006</v>
+        <v>1735528.3345000001</v>
       </c>
       <c r="M27">
-        <v>1542680.2972000006</v>
+        <v>1735528.3345000001</v>
       </c>
       <c r="N27">
         <v>1988879.4581600011</v>
       </c>
       <c r="O27">
-        <v>1988879.4581600011</v>
+        <v>1491667.5935</v>
       </c>
       <c r="P27">
-        <v>1988879.4581600011</v>
+        <v>2237501.3909999998</v>
       </c>
       <c r="Q27">
-        <v>1988879.4581600011</v>
+        <v>2237501.3909999998</v>
       </c>
       <c r="R27">
-        <v>1988879.4581600011</v>
+        <v>2237501.3909999998</v>
       </c>
       <c r="S27">
-        <v>1988879.4581600011</v>
+        <v>2237501.3909999998</v>
       </c>
       <c r="T27">
-        <v>88916.45</v>
+        <v>314897</v>
       </c>
       <c r="U27">
-        <v>88916.45</v>
+        <v>354132.33750000002</v>
       </c>
       <c r="V27">
-        <v>88916.45</v>
+        <v>531198.50624999998</v>
       </c>
       <c r="W27">
-        <v>88916.45</v>
+        <v>531198.50624999998</v>
       </c>
       <c r="X27">
-        <v>88916.45</v>
+        <v>531198.50624999998</v>
       </c>
       <c r="Y27">
-        <v>88916.45</v>
+        <v>531198.50624999998</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
@@ -6764,73 +6186,73 @@
         <v>204050.9535</v>
       </c>
       <c r="C28">
-        <v>204050.9535</v>
+        <v>153038.21512499999</v>
       </c>
       <c r="D28">
-        <v>204050.9535</v>
+        <v>229557.32264999999</v>
       </c>
       <c r="E28">
-        <v>204050.9535</v>
+        <v>229557.32264999999</v>
       </c>
       <c r="F28">
-        <v>204050.9535</v>
+        <v>229557.32264999999</v>
       </c>
       <c r="G28">
-        <v>204050.9535</v>
+        <v>229557.32264999999</v>
       </c>
       <c r="H28">
         <v>1539811.0840000003</v>
       </c>
       <c r="I28">
-        <v>1539811.0840000003</v>
+        <v>1154858.3130000001</v>
       </c>
       <c r="J28">
-        <v>1539811.0840000003</v>
+        <v>1732301.4694999999</v>
       </c>
       <c r="K28">
-        <v>1539811.0840000003</v>
+        <v>1732301.4694999999</v>
       </c>
       <c r="L28">
-        <v>1539811.0840000003</v>
+        <v>1732301.4694999999</v>
       </c>
       <c r="M28">
-        <v>1539811.0840000003</v>
+        <v>1732301.4694999999</v>
       </c>
       <c r="N28">
         <v>1977873.4631999999</v>
       </c>
       <c r="O28">
-        <v>1977873.4631999999</v>
+        <v>1483414.0972500001</v>
       </c>
       <c r="P28">
-        <v>1977873.4631999999</v>
+        <v>2225121.145</v>
       </c>
       <c r="Q28">
-        <v>1977873.4631999999</v>
+        <v>2225121.145</v>
       </c>
       <c r="R28">
-        <v>1977873.4631999999</v>
+        <v>2225121.145</v>
       </c>
       <c r="S28">
-        <v>1977873.4631999999</v>
+        <v>2225121.145</v>
       </c>
       <c r="T28">
-        <v>87606.7</v>
+        <v>308477.99</v>
       </c>
       <c r="U28">
-        <v>87606.7</v>
+        <v>346737.73875000002</v>
       </c>
       <c r="V28">
-        <v>87606.7</v>
+        <v>520106.60820000002</v>
       </c>
       <c r="W28">
-        <v>87606.7</v>
+        <v>520106.60820000002</v>
       </c>
       <c r="X28">
-        <v>87606.7</v>
+        <v>520106.60820000002</v>
       </c>
       <c r="Y28">
-        <v>87606.7</v>
+        <v>520106.60820000002</v>
       </c>
     </row>
   </sheetData>
@@ -8684,4 +8106,247 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F60D7FF-52FE-4E9C-8C92-EE039FC68DFA}">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2027</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2028</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2029</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2030</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2031</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2032</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2033</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2034</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2035</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2036</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2037</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2038</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2039</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2040</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2041</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2042</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2043</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2044</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2045</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2046</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2047</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2048</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/scenario_specific_data.xlsx
+++ b/scenario_specific_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214930D9-C62F-4C29-88E9-B7A761B5F755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FAE03B-A020-4AC6-8C8A-0514E26264FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{135E7A19-983F-4672-B1BC-B86D20613CB6}"/>
   </bookViews>

--- a/scenario_specific_data.xlsx
+++ b/scenario_specific_data.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FAE03B-A020-4AC6-8C8A-0514E26264FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36193313-A02B-440F-A921-812EB06D1427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{135E7A19-983F-4672-B1BC-B86D20613CB6}"/>
+    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" xr2:uid="{135E7A19-983F-4672-B1BC-B86D20613CB6}"/>
   </bookViews>
   <sheets>
     <sheet name="import_prices" sheetId="1" r:id="rId1"/>
     <sheet name="manufacturing_prices" sheetId="5" r:id="rId2"/>
     <sheet name="piped_gas_prices" sheetId="2" r:id="rId3"/>
-    <sheet name="lng_prices" sheetId="3" r:id="rId4"/>
-    <sheet name="piped_gas_trajectory" sheetId="4" r:id="rId5"/>
-    <sheet name="elec_demand" sheetId="6" r:id="rId6"/>
+    <sheet name="piped_gas_trajectory" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>Stf</t>
   </si>
@@ -62,24 +60,6 @@
   </si>
   <si>
     <t>import_EU27_solarPV_2049</t>
-  </si>
-  <si>
-    <t>lng_2024</t>
-  </si>
-  <si>
-    <t>lng_2029</t>
-  </si>
-  <si>
-    <t>lng_2034</t>
-  </si>
-  <si>
-    <t>lng_2039</t>
-  </si>
-  <si>
-    <t>lng_2044</t>
-  </si>
-  <si>
-    <t>lng_2049</t>
   </si>
   <si>
     <t>piped_gas_2024</t>
@@ -246,24 +226,6 @@
   <si>
     <t>manufacturing_EU27_Batteries_2049</t>
   </si>
-  <si>
-    <t>elec_dem_2024</t>
-  </si>
-  <si>
-    <t>elec_dem_2029</t>
-  </si>
-  <si>
-    <t>elec_dem_2034</t>
-  </si>
-  <si>
-    <t>elec_dem_2039</t>
-  </si>
-  <si>
-    <t>elec_dem_2044</t>
-  </si>
-  <si>
-    <t>elec_dem_2049</t>
-  </si>
 </sst>
 </file>
 
@@ -278,18 +240,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -310,10 +266,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -817,433 +772,6 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>lng_prices!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Resulting</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>lng_prices!$A$2:$A$28</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
-                <c:pt idx="0">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2025</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2026</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2027</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2028</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2029</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2030</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2031</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2032</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2033</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2034</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2035</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2036</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2037</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2038</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2039</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2040</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2041</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2042</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2043</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2044</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2045</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2046</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2047</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2048</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2049</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2050</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>lng_prices!$H$2:$H$28</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
-                <c:pt idx="0">
-                  <c:v>23.62</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23.62</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>23.62</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.62</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.62</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>23.62</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>29.94</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>36.54</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>36.54</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-73B8-4ED3-B07D-29FCC6D3ED78}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="494675759"/>
-        <c:axId val="494679119"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="494675759"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-AT"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="494679119"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="494679119"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-AT"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="494675759"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-AT"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-AT"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
               <c:f>piped_gas_trajectory!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -1657,46 +1185,6 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2768,522 +2256,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3326,47 +2298,6 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>130492</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>5715</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>155257</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Diagramm 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7E2525F-13C4-560D-E608-08603823BF43}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3753,58 +2684,58 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
+      <c r="O1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" t="s">
+      <c r="P1" t="s">
         <v>28</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>29</v>
       </c>
-      <c r="L1" t="s">
+      <c r="R1" t="s">
         <v>30</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="T1" t="s">
         <v>32</v>
       </c>
-      <c r="O1" t="s">
+      <c r="U1" t="s">
         <v>33</v>
       </c>
-      <c r="P1" t="s">
+      <c r="V1" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="W1" t="s">
         <v>35</v>
       </c>
-      <c r="R1" t="s">
+      <c r="X1" t="s">
         <v>36</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Y1" t="s">
         <v>37</v>
-      </c>
-      <c r="T1" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" t="s">
-        <v>39</v>
-      </c>
-      <c r="V1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -4056,7 +2987,7 @@
       <c r="I12">
         <v>1037009.3408</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="3">
         <v>987009.34</v>
       </c>
       <c r="N12">
@@ -4097,7 +3028,7 @@
       <c r="I13">
         <v>1035096.532</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>1477644.798</v>
       </c>
       <c r="N13">
@@ -4138,7 +3069,7 @@
       <c r="I14">
         <v>1033183.7232</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="3">
         <v>1474775.5848000001</v>
       </c>
       <c r="N14">
@@ -4179,7 +3110,7 @@
       <c r="I15">
         <v>1031270.9144</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="3">
         <v>1471906.3716</v>
       </c>
       <c r="N15">
@@ -4220,7 +3151,7 @@
       <c r="I16">
         <v>1029358.1056</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="3">
         <v>1469037.1584000001</v>
       </c>
       <c r="N16">
@@ -4264,10 +3195,10 @@
       <c r="I17">
         <v>1027445.2968</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="3">
         <v>1466167.9452</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="3">
         <v>1466167.9452</v>
       </c>
       <c r="N17">
@@ -4317,10 +3248,10 @@
       <c r="I18">
         <v>1025532.488</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="3">
         <v>1463298.7320000001</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="3">
         <v>1463298.7320000001</v>
       </c>
       <c r="N18">
@@ -4370,10 +3301,10 @@
       <c r="I19">
         <v>1023619.6792</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="3">
         <v>1460429.52</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="3">
         <v>1460429.52</v>
       </c>
       <c r="N19">
@@ -4423,10 +3354,10 @@
       <c r="I20">
         <v>1021706.8704</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="3">
         <v>1457560.3056000001</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="3">
         <v>1457560.3056000001</v>
       </c>
       <c r="N20">
@@ -4476,10 +3407,10 @@
       <c r="I21">
         <v>1019794.0616</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="3">
         <v>1454691.0924</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="3">
         <v>1454691.0924</v>
       </c>
       <c r="N21">
@@ -4532,13 +3463,13 @@
       <c r="I22">
         <v>1017881.2528</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="3">
         <v>1451821.8792000001</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="3">
         <v>1451821.8792000001</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="3">
         <v>1451821.8792000001</v>
       </c>
       <c r="N22">
@@ -4597,13 +3528,13 @@
       <c r="I23">
         <v>1015968.444</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="3">
         <v>1448952.666</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="3">
         <v>1448952.666</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="3">
         <v>1448952.666</v>
       </c>
       <c r="N23">
@@ -4662,13 +3593,13 @@
       <c r="I24">
         <v>1014055.6352</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="3">
         <v>1446083.4528000001</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="3">
         <v>1446083.4528000001</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="3">
         <v>1446083.4528000001</v>
       </c>
       <c r="N24">
@@ -4727,13 +3658,13 @@
       <c r="I25">
         <v>1012142.8264</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="3">
         <v>1443214.2396</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="3">
         <v>1443214.2396</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="3">
         <v>1443214.2396</v>
       </c>
       <c r="N25">
@@ -4792,13 +3723,13 @@
       <c r="I26">
         <v>1010230.0176</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="3">
         <v>1440345.0264000001</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K26" s="3">
         <v>1440345.0264000001</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="3">
         <v>1440345.0264000001</v>
       </c>
       <c r="N26">
@@ -4860,16 +3791,16 @@
       <c r="I27">
         <v>1008317.2088</v>
       </c>
-      <c r="J27" s="4">
+      <c r="J27" s="3">
         <v>1437475.8132</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="3">
         <v>1437475.8132</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="3">
         <v>1437475.8132</v>
       </c>
-      <c r="M27" s="4">
+      <c r="M27" s="3">
         <v>1437475.8132</v>
       </c>
       <c r="N27">
@@ -4937,16 +3868,16 @@
       <c r="I28">
         <v>1006404.4</v>
       </c>
-      <c r="J28" s="4">
+      <c r="J28" s="3">
         <v>1434606.6</v>
       </c>
-      <c r="K28" s="4">
+      <c r="K28" s="3">
         <v>1434606.6</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28" s="3">
         <v>1434606.6</v>
       </c>
-      <c r="M28" s="4">
+      <c r="M28" s="3">
         <v>1434606.6</v>
       </c>
       <c r="N28">
@@ -5000,80 +3931,80 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -6270,25 +5201,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -6298,11 +5229,11 @@
       <c r="B2">
         <v>22.68</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2">
         <f>B2</f>
         <v>22.68</v>
@@ -6315,11 +5246,11 @@
       <c r="B3">
         <v>22.68</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3">
         <f t="shared" ref="H3:H5" si="0">B3</f>
         <v>22.68</v>
@@ -6332,11 +5263,11 @@
       <c r="B4">
         <v>22.68</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4">
         <f t="shared" si="0"/>
         <v>22.68</v>
@@ -6349,11 +5280,11 @@
       <c r="B5">
         <v>22.68</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
       <c r="H5">
         <f t="shared" si="0"/>
         <v>22.68</v>
@@ -6366,11 +5297,11 @@
       <c r="B6">
         <v>22.68</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6">
         <f>B6</f>
         <v>22.68</v>
@@ -6386,10 +5317,10 @@
       <c r="C7">
         <v>22.68</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7">
         <f>C7</f>
         <v>22.68</v>
@@ -6405,10 +5336,10 @@
       <c r="C8">
         <v>22.68</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8">
         <f t="shared" ref="H8:H10" si="1">C8</f>
         <v>22.68</v>
@@ -6424,10 +5355,10 @@
       <c r="C9">
         <v>22.68</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9">
         <f t="shared" si="1"/>
         <v>22.68</v>
@@ -6443,10 +5374,10 @@
       <c r="C10">
         <v>22.68</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
       <c r="H10">
         <f t="shared" si="1"/>
         <v>22.68</v>
@@ -6462,10 +5393,10 @@
       <c r="C11">
         <v>22.68</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
       <c r="H11">
         <f>C11</f>
         <v>22.68</v>
@@ -6484,9 +5415,9 @@
       <c r="D12">
         <v>22.68</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
       <c r="H12">
         <f>D12</f>
         <v>22.68</v>
@@ -6505,9 +5436,9 @@
       <c r="D13">
         <v>22.68</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
       <c r="H13">
         <f t="shared" ref="H13:H16" si="2">D13</f>
         <v>22.68</v>
@@ -6526,9 +5457,9 @@
       <c r="D14">
         <v>22.68</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
       <c r="H14">
         <f t="shared" si="2"/>
         <v>22.68</v>
@@ -6547,9 +5478,9 @@
       <c r="D15">
         <v>22.68</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
       <c r="H15">
         <f t="shared" si="2"/>
         <v>22.68</v>
@@ -6568,9 +5499,9 @@
       <c r="D16">
         <v>22.68</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
       <c r="H16">
         <f t="shared" si="2"/>
         <v>22.68</v>
@@ -6592,8 +5523,8 @@
       <c r="E17">
         <v>22.68</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
       <c r="H17">
         <f>E17</f>
         <v>22.68</v>
@@ -6615,8 +5546,8 @@
       <c r="E18">
         <v>20.52</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
       <c r="H18">
         <f t="shared" ref="H18:H21" si="3">E18</f>
         <v>20.52</v>
@@ -6638,8 +5569,8 @@
       <c r="E19">
         <v>20.52</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
       <c r="H19">
         <f t="shared" si="3"/>
         <v>20.52</v>
@@ -6661,8 +5592,8 @@
       <c r="E20">
         <v>20.52</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
       <c r="H20">
         <f t="shared" si="3"/>
         <v>20.52</v>
@@ -6684,8 +5615,8 @@
       <c r="E21">
         <v>20.52</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
       <c r="H21">
         <f t="shared" si="3"/>
         <v>20.52</v>
@@ -6710,7 +5641,7 @@
       <c r="F22">
         <v>20.52</v>
       </c>
-      <c r="G22" s="2"/>
+      <c r="G22" s="1"/>
       <c r="H22">
         <f>F22</f>
         <v>20.52</v>
@@ -6735,7 +5666,7 @@
       <c r="F23">
         <v>20.52</v>
       </c>
-      <c r="G23" s="2"/>
+      <c r="G23" s="1"/>
       <c r="H23">
         <f t="shared" ref="H23:H26" si="4">F23</f>
         <v>20.52</v>
@@ -6760,7 +5691,7 @@
       <c r="F24">
         <v>20.52</v>
       </c>
-      <c r="G24" s="2"/>
+      <c r="G24" s="1"/>
       <c r="H24">
         <f t="shared" si="4"/>
         <v>20.52</v>
@@ -6785,7 +5716,7 @@
       <c r="F25">
         <v>20.52</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" s="1"/>
       <c r="H25">
         <f t="shared" si="4"/>
         <v>20.52</v>
@@ -6810,7 +5741,7 @@
       <c r="F26">
         <v>20.52</v>
       </c>
-      <c r="G26" s="2"/>
+      <c r="G26" s="1"/>
       <c r="H26">
         <f t="shared" si="4"/>
         <v>20.52</v>
@@ -6877,622 +5808,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B22E9F6-210C-4B51-BC39-95E792B1A10E}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="B2" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2">
-        <f>B2</f>
-        <v>23.62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2025</v>
-      </c>
-      <c r="B3" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3">
-        <f t="shared" ref="H3:H5" si="0">B3</f>
-        <v>23.62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4">
-        <f t="shared" si="0"/>
-        <v>23.62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2027</v>
-      </c>
-      <c r="B5" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>23.62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>2028</v>
-      </c>
-      <c r="B6" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6">
-        <f>B6</f>
-        <v>23.62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2029</v>
-      </c>
-      <c r="B7" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="C7" s="1">
-        <v>23.62</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7">
-        <f>C7</f>
-        <v>23.62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2030</v>
-      </c>
-      <c r="B8" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C8" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8">
-        <f t="shared" ref="H8:H10" si="1">C8</f>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>2031</v>
-      </c>
-      <c r="B9" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C9" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9">
-        <f t="shared" si="1"/>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>2032</v>
-      </c>
-      <c r="B10" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C10" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10">
-        <f t="shared" si="1"/>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>2033</v>
-      </c>
-      <c r="B11" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C11" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11">
-        <f>C11</f>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>2034</v>
-      </c>
-      <c r="B12" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C12" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D12" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12">
-        <f>D12</f>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>2035</v>
-      </c>
-      <c r="B13" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C13" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D13" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13">
-        <f t="shared" ref="H13:H16" si="2">D13</f>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>2036</v>
-      </c>
-      <c r="B14" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C14" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D14" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14">
-        <f t="shared" si="2"/>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2037</v>
-      </c>
-      <c r="B15" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C15" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D15" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15">
-        <f t="shared" si="2"/>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>2038</v>
-      </c>
-      <c r="B16" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C16" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D16" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16">
-        <f t="shared" si="2"/>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>2039</v>
-      </c>
-      <c r="B17" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="C17" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="D17" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="E17" s="1">
-        <v>29.94</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17">
-        <f>E17</f>
-        <v>29.94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>2040</v>
-      </c>
-      <c r="B18" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C18" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D18" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E18" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18">
-        <f t="shared" ref="H18:H21" si="3">E18</f>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>2041</v>
-      </c>
-      <c r="B19" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C19" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D19" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E19" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19">
-        <f t="shared" si="3"/>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>2042</v>
-      </c>
-      <c r="B20" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C20" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D20" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E20" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20">
-        <f t="shared" si="3"/>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>2043</v>
-      </c>
-      <c r="B21" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C21" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D21" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E21" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21">
-        <f t="shared" si="3"/>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>2044</v>
-      </c>
-      <c r="B22" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C22" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D22" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E22" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F22" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22">
-        <f>F22</f>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>2045</v>
-      </c>
-      <c r="B23" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C23" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D23" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E23" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F23" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23">
-        <f t="shared" ref="H23:H26" si="4">F23</f>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>2046</v>
-      </c>
-      <c r="B24" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C24" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D24" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E24" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F24" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24">
-        <f t="shared" si="4"/>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>2047</v>
-      </c>
-      <c r="B25" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C25" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D25" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E25" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F25" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25">
-        <f t="shared" si="4"/>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>2048</v>
-      </c>
-      <c r="B26" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C26" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D26" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E26" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F26" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26">
-        <f t="shared" si="4"/>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>2049</v>
-      </c>
-      <c r="B27" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C27" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D27" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E27" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F27" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="G27" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="H27">
-        <f>G27</f>
-        <v>36.54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>2050</v>
-      </c>
-      <c r="B28" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="C28" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="D28" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="E28" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="F28" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="G28" s="1">
-        <v>36.54</v>
-      </c>
-      <c r="H28">
-        <f>G28</f>
-        <v>36.54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F4AA74-F6E7-4E96-8A8A-2DCFA03A93AC}">
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7502,25 +5817,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -7530,11 +5845,11 @@
       <c r="B2">
         <v>319200000</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2">
         <f>B2</f>
         <v>319200000</v>
@@ -7547,11 +5862,11 @@
       <c r="B3">
         <v>319200000</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3">
         <f t="shared" ref="H3:H5" si="0">B3</f>
         <v>319200000</v>
@@ -7564,11 +5879,11 @@
       <c r="B4">
         <v>319200000</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4">
         <f t="shared" si="0"/>
         <v>319200000</v>
@@ -7581,11 +5896,11 @@
       <c r="B5">
         <v>319200000</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
       <c r="H5">
         <f t="shared" si="0"/>
         <v>319200000</v>
@@ -7598,11 +5913,11 @@
       <c r="B6">
         <v>319200000</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6">
         <f>B6</f>
         <v>319200000</v>
@@ -7618,10 +5933,10 @@
       <c r="C7">
         <v>319200000</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7">
         <f>C7</f>
         <v>319200000</v>
@@ -7637,10 +5952,10 @@
       <c r="C8">
         <v>319200000</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8">
         <f t="shared" ref="H8:H10" si="1">C8</f>
         <v>319200000</v>
@@ -7656,10 +5971,10 @@
       <c r="C9">
         <v>319200000</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9">
         <f t="shared" si="1"/>
         <v>319200000</v>
@@ -7675,10 +5990,10 @@
       <c r="C10">
         <v>319200000</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
       <c r="H10">
         <f t="shared" si="1"/>
         <v>319200000</v>
@@ -7694,10 +6009,10 @@
       <c r="C11">
         <v>319200000</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
       <c r="H11">
         <f>C11</f>
         <v>319200000</v>
@@ -7716,9 +6031,9 @@
       <c r="D12">
         <v>319200000</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
       <c r="H12">
         <f>D12</f>
         <v>319200000</v>
@@ -7737,9 +6052,9 @@
       <c r="D13">
         <v>319200000</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
       <c r="H13">
         <f t="shared" ref="H13:H16" si="2">D13</f>
         <v>319200000</v>
@@ -7758,9 +6073,9 @@
       <c r="D14">
         <v>319200000</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
       <c r="H14">
         <f t="shared" si="2"/>
         <v>319200000</v>
@@ -7779,9 +6094,9 @@
       <c r="D15">
         <v>319200000</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
       <c r="H15">
         <f t="shared" si="2"/>
         <v>319200000</v>
@@ -7800,9 +6115,9 @@
       <c r="D16">
         <v>319200000</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
       <c r="H16">
         <f t="shared" si="2"/>
         <v>319200000</v>
@@ -7824,8 +6139,8 @@
       <c r="E17">
         <v>319200000</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
       <c r="H17">
         <f>E17</f>
         <v>319200000</v>
@@ -7847,8 +6162,8 @@
       <c r="E18">
         <v>319200000</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
       <c r="H18">
         <f t="shared" ref="H18:H21" si="3">E18</f>
         <v>319200000</v>
@@ -7870,8 +6185,8 @@
       <c r="E19">
         <v>319200000</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
       <c r="H19">
         <f t="shared" si="3"/>
         <v>319200000</v>
@@ -7893,8 +6208,8 @@
       <c r="E20">
         <v>319200000</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
       <c r="H20">
         <f t="shared" si="3"/>
         <v>319200000</v>
@@ -7916,8 +6231,8 @@
       <c r="E21">
         <v>319200000</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
       <c r="H21">
         <f t="shared" si="3"/>
         <v>319200000</v>
@@ -7942,7 +6257,7 @@
       <c r="F22">
         <v>319200000</v>
       </c>
-      <c r="G22" s="2"/>
+      <c r="G22" s="1"/>
       <c r="H22">
         <f>F22</f>
         <v>319200000</v>
@@ -7967,7 +6282,7 @@
       <c r="F23">
         <v>319200000</v>
       </c>
-      <c r="G23" s="2"/>
+      <c r="G23" s="1"/>
       <c r="H23">
         <f t="shared" ref="H23:H26" si="4">F23</f>
         <v>319200000</v>
@@ -7992,7 +6307,7 @@
       <c r="F24">
         <v>319200000</v>
       </c>
-      <c r="G24" s="2"/>
+      <c r="G24" s="1"/>
       <c r="H24">
         <f t="shared" si="4"/>
         <v>319200000</v>
@@ -8017,7 +6332,7 @@
       <c r="F25">
         <v>319200000</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" s="1"/>
       <c r="H25">
         <f t="shared" si="4"/>
         <v>319200000</v>
@@ -8042,7 +6357,7 @@
       <c r="F26">
         <v>319200000</v>
       </c>
-      <c r="G26" s="2"/>
+      <c r="G26" s="1"/>
       <c r="H26">
         <f t="shared" si="4"/>
         <v>319200000</v>
@@ -8106,247 +6421,4 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F60D7FF-52FE-4E9C-8C92-EE039FC68DFA}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2025</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2026</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2027</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>2028</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2029</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2030</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>2031</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>2032</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>2033</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>2034</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>2035</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>2036</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2037</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>2038</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>2039</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>2040</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>2041</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>2042</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>2043</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>2044</v>
-      </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>2045</v>
-      </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>2046</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>2047</v>
-      </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>2048</v>
-      </c>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>2050</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>